--- a/results/exp01-svhn-vgg11-e8-fedrolex/20260921-212154/rounds.xlsx
+++ b/results/exp01-svhn-vgg11-e8-fedrolex/20260921-212154/rounds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U28"/>
+  <dimension ref="A1:U101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2776,6 +2776,6065 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-09-21 21:54:35</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.6339693169816729</v>
+      </c>
+      <c r="F29" t="n">
+        <v>87.28488014751076</v>
+      </c>
+      <c r="G29" t="n">
+        <v>92.32098955132145</v>
+      </c>
+      <c r="H29" t="n">
+        <v>20</v>
+      </c>
+      <c r="I29" t="n">
+        <v>70.0498</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>1:10.05</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>66.1579</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.1281</v>
+      </c>
+      <c r="M29" t="n">
+        <v>2.7631</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1960.8119</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>32:40.81</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>6,9,0,8,2,5,1,3,4,7</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>6:29;9:49;0:47;8:29;2:10;5:33;1:25;3:12;4:10;7:10</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>6:[0,7];9:[3,4,5,6];0:[3,4,5,6];8:[3,4];2:[0];5:[0,6,7];1:[2,3];3:[7];4:[3];7:[1]</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>c6:bw=29,experts=[0,7]; c9:bw=49,experts=[3,4,5,6]; c0:bw=47,experts=[3,4,5,6]; c8:bw=29,experts=[3,4]; c2:bw=10,experts=[0]; c5:bw=33,experts=[0,6,7]; c1:bw=25,experts=[2,3]; c3:bw=12,experts=[7]; c4:bw=10,experts=[3]; c7:bw=10,experts=[1]</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>9.6752,3.5233,4.6645,2.8446,8.9206,2.5790,11.4271,1.3894,7.5336,13.6006</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-09-21 21:55:44</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.6296445069139842</v>
+      </c>
+      <c r="F30" t="n">
+        <v>91.74093423478796</v>
+      </c>
+      <c r="G30" t="n">
+        <v>92.32098955132145</v>
+      </c>
+      <c r="H30" t="n">
+        <v>20</v>
+      </c>
+      <c r="I30" t="n">
+        <v>69.1071</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>1:09.11</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>65.1888</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.2264</v>
+      </c>
+      <c r="M30" t="n">
+        <v>2.6911</v>
+      </c>
+      <c r="N30" t="n">
+        <v>2029.9372</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>33:49.94</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>4,0,1,9,6,8,7,3,2,5</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>4:38;0:44;1:33;9:44;6:43;8:34;7:21;3:32;2:18;5:33</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>4:[4,5,6];0:[0,1,2,7];1:[4,5,6];9:[0,1,2,7];6:[1,2,3,4];8:[5,6,7];7:[2,3];3:[0,1,2];2:[1];5:[1,2,3]</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>c4:bw=38,experts=[4,5,6]; c0:bw=44,experts=[0,1,2,7]; c1:bw=33,experts=[4,5,6]; c9:bw=44,experts=[0,1,2,7]; c6:bw=43,experts=[1,2,3,4]; c8:bw=34,experts=[5,6,7]; c7:bw=21,experts=[2,3]; c3:bw=32,experts=[0,1,2]; c2:bw=18,experts=[1]; c5:bw=33,experts=[1,2,3]</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>7.5828,4.4041,12.2128,3.3108,9.6575,2.9200,12.9221,1.4166,8.2659,2.4963</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-09-21 21:56:54</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.6232742523705401</v>
+      </c>
+      <c r="F31" t="n">
+        <v>91.01106330669944</v>
+      </c>
+      <c r="G31" t="n">
+        <v>92.32098955132145</v>
+      </c>
+      <c r="H31" t="n">
+        <v>20</v>
+      </c>
+      <c r="I31" t="n">
+        <v>69.5017</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>1:09.50</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>65.5672</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.2197</v>
+      </c>
+      <c r="M31" t="n">
+        <v>2.7139</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2099.6602</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>34:59.66</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>5,1,9,4,0,8,6,7,3,2</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>5:62;1:35;9:54;4:51;0:17;8:41;6:11;7:12;3:59;2:27</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>5:[0,1,4,5,6,7];1:[0,1,7];9:[3,4,5,6,7];4:[0,1,2,3,7];0:[3];8:[0,1,2,3];6:[5];7:[4];3:[3,4,5,6,7];2:[2,3]</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>c5:bw=62,experts=[0,1,4,5,6,7]; c1:bw=35,experts=[0,1,7]; c9:bw=54,experts=[3,4,5,6,7]; c4:bw=51,experts=[0,1,2,3,7]; c0:bw=17,experts=[3]; c8:bw=41,experts=[0,1,2,3]; c6:bw=11,experts=[5]; c7:bw=12,experts=[4]; c3:bw=59,experts=[3,4,5,6,7]; c2:bw=27,experts=[2,3]</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>2.5902,11.5014,3.5230,7.5735,4.6500,2.8393,9.6250,13.3083,1.4059,8.5506</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-09-21 21:58:03</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.6243608123745574</v>
+      </c>
+      <c r="F32" t="n">
+        <v>92.27873386601107</v>
+      </c>
+      <c r="G32" t="n">
+        <v>92.32098955132145</v>
+      </c>
+      <c r="H32" t="n">
+        <v>20</v>
+      </c>
+      <c r="I32" t="n">
+        <v>68.8087</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>1:08.81</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>64.86660000000001</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.1911</v>
+      </c>
+      <c r="M32" t="n">
+        <v>2.7502</v>
+      </c>
+      <c r="N32" t="n">
+        <v>2168.4881</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>36:08.49</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>6,4,9,1,5,8,3,2,0,7</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>6:29;4:19;9:45;1:30;5:62;8:33;3:24;2:15;0:47;7:63</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>6:[6,7];4:[4];9:[0,1,2,3];1:[2,3,4];5:[2,3,4,5,6,7];8:[4,5,6];3:[0,1];2:[4];0:[4,5,6,7];7:[0,1,2,5,6,7]</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>c6:bw=29,experts=[6,7]; c4:bw=19,experts=[4]; c9:bw=45,experts=[0,1,2,3]; c1:bw=30,experts=[2,3,4]; c5:bw=62,experts=[2,3,4,5,6,7]; c8:bw=33,experts=[4,5,6]; c3:bw=24,experts=[0,1]; c2:bw=15,experts=[4]; c0:bw=47,experts=[4,5,6,7]; c7:bw=63,experts=[0,1,2,5,6,7]</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>9.6363,7.5515,3.2830,12.1102,2.4884,2.8930,1.3838,8.2215,4.3801,12.9187</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-09-21 21:59:12</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.6221315746881658</v>
+      </c>
+      <c r="F33" t="n">
+        <v>90.80362630608482</v>
+      </c>
+      <c r="G33" t="n">
+        <v>92.32098955132145</v>
+      </c>
+      <c r="H33" t="n">
+        <v>20</v>
+      </c>
+      <c r="I33" t="n">
+        <v>69.2743</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>1:09.27</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>65.3086</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.2094</v>
+      </c>
+      <c r="M33" t="n">
+        <v>2.7555</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2237.7818</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>37:17.78</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>8,5,4,7,0,1,3,6,2,9</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>8:21;5:36;4:49;7:47;0:46;1:21;3:28;6:27;2:54;9:31</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>8:[0,7];5:[0,1,2];4:[0,5,6,7];7:[3,4,5,6];0:[0,1,2,3];1:[5,6];3:[2,3];6:[0,1];2:[0,1,5,6,7];9:[4,5,6]</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>c8:bw=21,experts=[0,7]; c5:bw=36,experts=[0,1,2]; c4:bw=49,experts=[0,5,6,7]; c7:bw=47,experts=[3,4,5,6]; c0:bw=46,experts=[0,1,2,3]; c1:bw=21,experts=[5,6]; c3:bw=28,experts=[2,3]; c6:bw=27,experts=[0,1]; c2:bw=54,experts=[0,1,5,6,7]; c9:bw=31,experts=[4,5,6]</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>2.8370,2.5010,7.5612,13.7288,4.7337,11.3319,1.3921,9.6078,8.3415,3.2737</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:00:20</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.6197697105545935</v>
+      </c>
+      <c r="F34" t="n">
+        <v>93.86524277811924</v>
+      </c>
+      <c r="G34" t="n">
+        <v>93.86524277811924</v>
+      </c>
+      <c r="H34" t="n">
+        <v>33</v>
+      </c>
+      <c r="I34" t="n">
+        <v>68.52719999999999</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>1:08.53</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>64.4717</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1.3291</v>
+      </c>
+      <c r="M34" t="n">
+        <v>2.7257</v>
+      </c>
+      <c r="N34" t="n">
+        <v>2306.3285</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>38:26.33</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>7,1,3,6,5,9,2,8,4,0</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>7:52;1:34;3:70;6:37;5:29;9:42;2:24;8:50;4:45;0:62</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>7:[0,1,2,3,7];1:[0,1,7];3:[0,1,2,4,5,6,7];6:[2,3,4];5:[3,4];9:[0,1,2,7];2:[2,3];8:[1,2,3,4,5];4:[1,2,3,4];0:[0,1,4,5,6,7]</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>c7:bw=52,experts=[0,1,2,3,7]; c1:bw=34,experts=[0,1,7]; c3:bw=70,experts=[0,1,2,4,5,6,7]; c6:bw=37,experts=[2,3,4]; c5:bw=29,experts=[3,4]; c9:bw=42,experts=[0,1,2,7]; c2:bw=24,experts=[2,3]; c8:bw=50,experts=[1,2,3,4,5]; c4:bw=45,experts=[1,2,3,4]; c0:bw=62,experts=[0,1,4,5,6,7]</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>13.0306,11.5990,1.4028,9.6166,2.4866,3.2749,8.2407,2.8535,7.5738,4.3930</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:01:30</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.6183112279888401</v>
+      </c>
+      <c r="F35" t="n">
+        <v>92.72049784880147</v>
+      </c>
+      <c r="G35" t="n">
+        <v>93.86524277811924</v>
+      </c>
+      <c r="H35" t="n">
+        <v>33</v>
+      </c>
+      <c r="I35" t="n">
+        <v>69.08839999999999</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>1:09.09</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>64.9378</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1.373</v>
+      </c>
+      <c r="M35" t="n">
+        <v>2.7767</v>
+      </c>
+      <c r="N35" t="n">
+        <v>2375.4371</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>39:35.44</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>4,1,6,9,8,0,5,7,3,2</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>4:46;1:46;6:48;9:68;8:42;0:22;5:60;7:32;3:72;2:54</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>4:[0,5,6,7];1:[2,3,4,5];6:[0,5,6,7];9:[0,3,4,5,6,7];8:[0,1,6,7];0:[2,3];5:[0,1,2,5,6,7];7:[4,5,6];3:[0,1,3,4,5,6,7];2:[0,4,5,6,7]</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>c4:bw=46,experts=[0,5,6,7]; c1:bw=46,experts=[2,3,4,5]; c6:bw=48,experts=[0,5,6,7]; c9:bw=68,experts=[0,3,4,5,6,7]; c8:bw=42,experts=[0,1,6,7]; c0:bw=22,experts=[2,3]; c5:bw=60,experts=[0,1,2,5,6,7]; c7:bw=32,experts=[4,5,6]; c3:bw=72,experts=[0,1,3,4,5,6,7]; c2:bw=54,experts=[0,4,5,6,7]</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>7.6082,11.4769,9.7140,3.4435,2.8446,4.5153,2.4964,12.9147,1.3996,8.5246</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:02:38</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.6166629481255548</v>
+      </c>
+      <c r="F36" t="n">
+        <v>93.6539643515673</v>
+      </c>
+      <c r="G36" t="n">
+        <v>93.86524277811924</v>
+      </c>
+      <c r="H36" t="n">
+        <v>33</v>
+      </c>
+      <c r="I36" t="n">
+        <v>68.718</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>1:08.72</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>64.69289999999999</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1.2469</v>
+      </c>
+      <c r="M36" t="n">
+        <v>2.7773</v>
+      </c>
+      <c r="N36" t="n">
+        <v>2444.1752</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>40:44.18</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>4,0,1,6,2,8,9,7,5,3</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>4:33;0:20;1:31;6:44;2:46;8:50;9:27;7:48;5:41;3:24</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>4:[1,2,3];0:[4,5];1:[0,6,7];6:[1,2,3,4];2:[1,2,3,4];8:[2,3,4,5,6];9:[1,2];7:[0,1,2,7];5:[3,4,5,6];3:[2,3]</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>c4:bw=33,experts=[1,2,3]; c0:bw=20,experts=[4,5]; c1:bw=31,experts=[0,6,7]; c6:bw=44,experts=[1,2,3,4]; c2:bw=46,experts=[1,2,3,4]; c8:bw=50,experts=[2,3,4,5,6]; c9:bw=27,experts=[1,2]; c7:bw=48,experts=[0,1,2,7]; c5:bw=41,experts=[3,4,5,6]; c3:bw=24,experts=[2,3]</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>7.5884,4.4112,11.8727,9.6993,8.2720,2.8380,3.2505,12.8762,2.4860,1.3985</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:03:47</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.614955403997038</v>
+      </c>
+      <c r="F37" t="n">
+        <v>93.00092194222495</v>
+      </c>
+      <c r="G37" t="n">
+        <v>93.86524277811924</v>
+      </c>
+      <c r="H37" t="n">
+        <v>33</v>
+      </c>
+      <c r="I37" t="n">
+        <v>68.2582</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>1:08.26</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>64.1644</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1.3018</v>
+      </c>
+      <c r="M37" t="n">
+        <v>2.7912</v>
+      </c>
+      <c r="N37" t="n">
+        <v>2512.4545</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>41:52.45</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>9,0,3,7,6,5,1,4,8,2</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>9:37;0:36;3:60;7:27;6:43;5:49;1:10;4:74;8:51;2:50</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>9:[3,4,5];0:[0,6,7];3:[0,1,4,5,6,7];7:[3,4];6:[0,5,6,7];5:[0,1,2,7];1:[1];4:[0,1,2,4,5,6,7];8:[0,1,2,3,7];2:[0,1,5,6,7]</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>c9:bw=37,experts=[3,4,5]; c0:bw=36,experts=[0,6,7]; c3:bw=60,experts=[0,1,4,5,6,7]; c7:bw=27,experts=[3,4]; c6:bw=43,experts=[0,5,6,7]; c5:bw=49,experts=[0,1,2,7]; c1:bw=10,experts=[1]; c4:bw=74,experts=[0,1,2,4,5,6,7]; c8:bw=51,experts=[0,1,2,3,7]; c2:bw=50,experts=[0,1,5,6,7]</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>3.2924,4.4211,1.3895,12.8939,9.6397,2.4885,11.3452,7.5715,2.8504,8.2724</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:04:56</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.6127642665418902</v>
+      </c>
+      <c r="F38" t="n">
+        <v>93.75</v>
+      </c>
+      <c r="G38" t="n">
+        <v>93.86524277811924</v>
+      </c>
+      <c r="H38" t="n">
+        <v>33</v>
+      </c>
+      <c r="I38" t="n">
+        <v>68.9406</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>1:08.94</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>64.91970000000001</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1.237</v>
+      </c>
+      <c r="M38" t="n">
+        <v>2.7831</v>
+      </c>
+      <c r="N38" t="n">
+        <v>2581.4159</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>43:01.42</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>1,5,2,6,4,7,9,0,3,8</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>1:18;5:39;2:36;6:65;4:39;7:42;9:40;0:54;3:36;8:10</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>1:[2];5:[3,4,5];2:[2,3,4];6:[1,2,3,4,5,6];4:[3,4,5];7:[0,5,6,7];9:[0,1,6,7];0:[1,2,3,4,5];3:[2,3,4];8:[4]</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>c1:bw=18,experts=[2]; c5:bw=39,experts=[3,4,5]; c2:bw=36,experts=[2,3,4]; c6:bw=65,experts=[1,2,3,4,5,6]; c4:bw=39,experts=[3,4,5]; c7:bw=42,experts=[0,5,6,7]; c9:bw=40,experts=[0,1,6,7]; c0:bw=54,experts=[1,2,3,4,5]; c3:bw=36,experts=[2,3,4]; c8:bw=10,experts=[4]</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>12.1467,2.5038,8.2911,9.6741,7.5493,12.8877,3.2656,4.3753,1.3872,2.8388</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:06:04</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.6140836666349651</v>
+      </c>
+      <c r="F39" t="n">
+        <v>93.14305470190534</v>
+      </c>
+      <c r="G39" t="n">
+        <v>93.86524277811924</v>
+      </c>
+      <c r="H39" t="n">
+        <v>33</v>
+      </c>
+      <c r="I39" t="n">
+        <v>68.4435</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>1:08.44</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>64.44670000000001</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1.214</v>
+      </c>
+      <c r="M39" t="n">
+        <v>2.7821</v>
+      </c>
+      <c r="N39" t="n">
+        <v>2649.8806</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>44:09.88</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>8,6,4,1,5,2,3,7,9,0</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>8:46;6:17;4:52;1:31;5:10;2:10;3:38;7:51;9:26;0:40</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>8:[0,5,6,7];6:[7];4:[0,1,2,6,7];1:[3,4,5];5:[6];2:[5];3:[5,6,7];7:[1,2,3,4,5];9:[2,3];0:[0,1,6,7]</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>c8:bw=46,experts=[0,5,6,7]; c6:bw=17,experts=[7]; c4:bw=52,experts=[0,1,2,6,7]; c1:bw=31,experts=[3,4,5]; c5:bw=10,experts=[6]; c2:bw=10,experts=[5]; c3:bw=38,experts=[5,6,7]; c7:bw=51,experts=[1,2,3,4,5]; c9:bw=26,experts=[2,3]; c0:bw=40,experts=[0,1,6,7]</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>2.8547,9.9450,7.6205,11.4314,2.4745,8.2156,1.3899,12.8572,3.2603,4.3976</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:07:14</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.6110928632966631</v>
+      </c>
+      <c r="F40" t="n">
+        <v>92.49001229256299</v>
+      </c>
+      <c r="G40" t="n">
+        <v>93.86524277811924</v>
+      </c>
+      <c r="H40" t="n">
+        <v>33</v>
+      </c>
+      <c r="I40" t="n">
+        <v>69.624</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>1:09.62</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>65.57769999999999</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1.2422</v>
+      </c>
+      <c r="M40" t="n">
+        <v>2.8034</v>
+      </c>
+      <c r="N40" t="n">
+        <v>2719.5259</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>45:19.53</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>3,0,1,7,6,8,2,4,9,5</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>3:26;0:10;1:45;7:40;6:31;8:45;2:36;4:36;9:24;5:75</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>3:[0,1];0:[2];1:[0,1,6,7];7:[0,1,6,7];6:[0,1,2];8:[1,2,3,4];2:[0,6,7];4:[3,4,5];9:[4,5];5:[0,1,2,3,4,5,7]</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>c3:bw=26,experts=[0,1]; c0:bw=10,experts=[2]; c1:bw=45,experts=[0,1,6,7]; c7:bw=40,experts=[0,1,6,7]; c6:bw=31,experts=[0,1,2]; c8:bw=45,experts=[1,2,3,4]; c2:bw=36,experts=[0,6,7]; c4:bw=36,experts=[3,4,5]; c9:bw=24,experts=[4,5]; c5:bw=75,experts=[0,1,2,3,4,5,7]</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>1.4151,4.6273,11.4373,13.6291,9.6359,2.8503,8.6934,7.5551,3.2552,2.4789</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:08:23</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.611828928069421</v>
+      </c>
+      <c r="F41" t="n">
+        <v>91.75629993853718</v>
+      </c>
+      <c r="G41" t="n">
+        <v>93.86524277811924</v>
+      </c>
+      <c r="H41" t="n">
+        <v>33</v>
+      </c>
+      <c r="I41" t="n">
+        <v>68.8597</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>1:08.86</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="L41" t="n">
+        <v>1.234</v>
+      </c>
+      <c r="M41" t="n">
+        <v>2.8249</v>
+      </c>
+      <c r="N41" t="n">
+        <v>2788.4097</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>46:28.41</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>8,1,5,6,2,7,3,4,9,0</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>8:26;1:42;5:32;6:46;2:65;7:66;3:10;4:19;9:40;0:36</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>8:[5,6];1:[2,3,4,5];5:[0,6,7];6:[3,4,5,6];2:[1,2,3,4,5,6];7:[2,3,4,5,6,7];3:[2];4:[6];9:[0,1,6,7];0:[3,4,5]</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>c8:bw=26,experts=[5,6]; c1:bw=42,experts=[2,3,4,5]; c5:bw=32,experts=[0,6,7]; c6:bw=46,experts=[3,4,5,6]; c2:bw=65,experts=[1,2,3,4,5,6]; c7:bw=66,experts=[2,3,4,5,6,7]; c3:bw=10,experts=[2]; c4:bw=19,experts=[6]; c9:bw=40,experts=[0,1,6,7]; c0:bw=36,experts=[3,4,5]</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>2.8532,12.0231,2.5032,9.7487,8.2721,12.8629,1.3838,7.5247,3.2768,4.3514</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:09:31</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.6147714453676029</v>
+      </c>
+      <c r="F42" t="n">
+        <v>93.46957590657652</v>
+      </c>
+      <c r="G42" t="n">
+        <v>93.86524277811924</v>
+      </c>
+      <c r="H42" t="n">
+        <v>33</v>
+      </c>
+      <c r="I42" t="n">
+        <v>68.48779999999999</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>1:08.49</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>64.4388</v>
+      </c>
+      <c r="L42" t="n">
+        <v>1.2893</v>
+      </c>
+      <c r="M42" t="n">
+        <v>2.7589</v>
+      </c>
+      <c r="N42" t="n">
+        <v>2856.9198</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>47:36.92</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>2,6,8,1,4,5,7,3,9,0</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>2:54;6:10;8:57;1:10;4:50;5:61;7:68;3:40;9:54;0:10</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>2:[0,1,2,3,7];6:[7];8:[0,1,2,3,7];1:[6];4:[0,1,2,3,7];5:[1,2,3,4,5,6];7:[0,1,2,3,4,5];3:[3,4,5,6];9:[2,3,4,5,6];0:[6]</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>c2:bw=54,experts=[0,1,2,3,7]; c6:bw=10,experts=[7]; c8:bw=57,experts=[0,1,2,3,7]; c1:bw=10,experts=[6]; c4:bw=50,experts=[0,1,2,3,7]; c5:bw=61,experts=[1,2,3,4,5,6]; c7:bw=68,experts=[0,1,2,3,4,5]; c3:bw=40,experts=[3,4,5,6]; c9:bw=54,experts=[2,3,4,5,6]; c0:bw=10,experts=[6]</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>8.3286,9.7388,2.8608,11.4363,7.5972,2.4643,12.8858,1.3936,3.3516,4.3817</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:10:40</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.6079747704191665</v>
+      </c>
+      <c r="F43" t="n">
+        <v>93.87292562999386</v>
+      </c>
+      <c r="G43" t="n">
+        <v>93.87292562999386</v>
+      </c>
+      <c r="H43" t="n">
+        <v>42</v>
+      </c>
+      <c r="I43" t="n">
+        <v>68.9211</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>1:08.92</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>64.8719</v>
+      </c>
+      <c r="L43" t="n">
+        <v>1.2815</v>
+      </c>
+      <c r="M43" t="n">
+        <v>2.7669</v>
+      </c>
+      <c r="N43" t="n">
+        <v>2925.8635</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>48:45.86</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>5,1,3,9,6,0,7,4,8,2</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>5:50;1:49;3:48;9:51;6:34;0:15;7:20;4:55;8:42;2:40</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>5:[0,1,2,3,7];1:[0,1,2,7];3:[0,1,2,7];9:[0,1,2,3,7];6:[0,1,2];0:[7];7:[6,7];4:[0,4,5,6,7];8:[4,5,6,7];2:[4,5,6,7]</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>c5:bw=50,experts=[0,1,2,3,7]; c1:bw=49,experts=[0,1,2,7]; c3:bw=48,experts=[0,1,2,7]; c9:bw=51,experts=[0,1,2,3,7]; c6:bw=34,experts=[0,1,2]; c0:bw=15,experts=[7]; c7:bw=20,experts=[6,7]; c4:bw=55,experts=[0,4,5,6,7]; c8:bw=42,experts=[4,5,6,7]; c2:bw=40,experts=[4,5,6,7]</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>2.5363,11.6537,1.4079,3.3546,10.1328,4.3743,12.8495,7.5295,2.8279,8.2054</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:11:49</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.6075864984857062</v>
+      </c>
+      <c r="F44" t="n">
+        <v>89.23248309772588</v>
+      </c>
+      <c r="G44" t="n">
+        <v>93.87292562999386</v>
+      </c>
+      <c r="H44" t="n">
+        <v>42</v>
+      </c>
+      <c r="I44" t="n">
+        <v>69.22799999999999</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>1:09.23</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>65.2881</v>
+      </c>
+      <c r="L44" t="n">
+        <v>1.2415</v>
+      </c>
+      <c r="M44" t="n">
+        <v>2.6976</v>
+      </c>
+      <c r="N44" t="n">
+        <v>2995.1158</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>49:55.12</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>5,1,2,8,9,7,4,6,3,0</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>5:53;1:58;2:51;8:45;9:32;7:21;4:34;6:12;3:65;0:21</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>5:[0,4,5,6,7];1:[3,4,5,6,7];2:[0,1,2,3,4];8:[0,1,2,3];9:[4,5,6];7:[0,1];4:[1,2,3];6:[3];3:[0,3,4,5,6,7];0:[0,1]</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>c5:bw=53,experts=[0,4,5,6,7]; c1:bw=58,experts=[3,4,5,6,7]; c2:bw=51,experts=[0,1,2,3,4]; c8:bw=45,experts=[0,1,2,3]; c9:bw=32,experts=[4,5,6]; c7:bw=21,experts=[0,1]; c4:bw=34,experts=[1,2,3]; c6:bw=12,experts=[3]; c3:bw=65,experts=[0,3,4,5,6,7]; c0:bw=21,experts=[0,1]</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>2.6017,11.4595,8.5472,2.8463,3.3342,13.4385,7.5245,9.5567,1.3899,4.5896</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:12:58</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.6080011615030024</v>
+      </c>
+      <c r="F45" t="n">
+        <v>93.02397049784881</v>
+      </c>
+      <c r="G45" t="n">
+        <v>93.87292562999386</v>
+      </c>
+      <c r="H45" t="n">
+        <v>42</v>
+      </c>
+      <c r="I45" t="n">
+        <v>69.00449999999999</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>1:09.00</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>64.9824</v>
+      </c>
+      <c r="L45" t="n">
+        <v>1.2608</v>
+      </c>
+      <c r="M45" t="n">
+        <v>2.7605</v>
+      </c>
+      <c r="N45" t="n">
+        <v>3064.144</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>51:04.14</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>0,3,4,2,7,5,6,9,8,1</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>0:66;3:47;4:29;2:37;7:75;5:24;6:20;9:37;8:34;1:45</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>0:[2,3,4,5,6,7];3:[1,2,3,4];4:[4,5];2:[5,6,7];7:[0,2,3,4,5,6,7];5:[1,2];6:[4,5];9:[0,1,7];8:[4,5,6];1:[0,1,2,3]</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>c0:bw=66,experts=[2,3,4,5,6,7]; c3:bw=47,experts=[1,2,3,4]; c4:bw=29,experts=[4,5]; c2:bw=37,experts=[5,6,7]; c7:bw=75,experts=[0,2,3,4,5,6,7]; c5:bw=24,experts=[1,2]; c6:bw=20,experts=[4,5]; c9:bw=37,experts=[0,1,7]; c8:bw=34,experts=[4,5,6]; c1:bw=45,experts=[0,1,2,3]</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>4.4050,1.4086,7.5435,8.1986,12.9771,2.5199,9.8882,3.2904,2.8363,11.9148</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:09</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.605192091890588</v>
+      </c>
+      <c r="F46" t="n">
+        <v>91.17240319606638</v>
+      </c>
+      <c r="G46" t="n">
+        <v>93.87292562999386</v>
+      </c>
+      <c r="H46" t="n">
+        <v>42</v>
+      </c>
+      <c r="I46" t="n">
+        <v>70.1992</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>1:10.20</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>66.1319</v>
+      </c>
+      <c r="L46" t="n">
+        <v>1.3005</v>
+      </c>
+      <c r="M46" t="n">
+        <v>2.766</v>
+      </c>
+      <c r="N46" t="n">
+        <v>3134.3684</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>52:14.37</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>8,0,3,4,7,2,9,6,5,1</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>8:55;0:36;3:67;4:64;7:36;2:49;9:25;6:10;5:44;1:56</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>8:[0,1,2,3,7];0:[0,1,2];3:[0,1,2,5,6,7];4:[0,1,2,3,6,7];7:[1,2,3];2:[0,1,2,3];9:[2,3];6:[6];5:[3,4,5,6];1:[0,4,5,6,7]</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>c8:bw=55,experts=[0,1,2,3,7]; c0:bw=36,experts=[0,1,2]; c3:bw=67,experts=[0,1,2,5,6,7]; c4:bw=64,experts=[0,1,2,3,6,7]; c7:bw=36,experts=[1,2,3]; c2:bw=49,experts=[0,1,2,3]; c9:bw=25,experts=[2,3]; c6:bw=10,experts=[6]; c5:bw=44,experts=[3,4,5,6]; c1:bw=56,experts=[0,4,5,6,7]</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>2.8511,4.6257,1.4351,7.5979,13.6126,8.9011,3.4634,9.6450,2.5785,11.4215</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:15:17</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.6047193118549649</v>
+      </c>
+      <c r="F47" t="n">
+        <v>94.6220036877689</v>
+      </c>
+      <c r="G47" t="n">
+        <v>94.6220036877689</v>
+      </c>
+      <c r="H47" t="n">
+        <v>46</v>
+      </c>
+      <c r="I47" t="n">
+        <v>68.5437</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>1:08.54</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>64.5214</v>
+      </c>
+      <c r="L47" t="n">
+        <v>1.2876</v>
+      </c>
+      <c r="M47" t="n">
+        <v>2.734</v>
+      </c>
+      <c r="N47" t="n">
+        <v>3202.9351</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>53:22.94</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>9,3,6,1,4,5,2,8,0,7</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>9:37;3:27;6:39;1:41;4:64;5:41;2:57;8:39;0:55;7:28</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>9:[4,5,6];3:[3,4];6:[0,1,7];1:[1,2,3,4];4:[0,1,4,5,6,7];5:[0,1,2,7];2:[0,4,5,6,7];8:[4,5,6];0:[3,4,5,6,7];7:[4,5]</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>c9:bw=37,experts=[4,5,6]; c3:bw=27,experts=[3,4]; c6:bw=39,experts=[0,1,7]; c1:bw=41,experts=[1,2,3,4]; c4:bw=64,experts=[0,1,4,5,6,7]; c5:bw=41,experts=[0,1,2,7]; c2:bw=57,experts=[0,4,5,6,7]; c8:bw=39,experts=[4,5,6]; c0:bw=55,experts=[3,4,5,6,7]; c7:bw=28,experts=[4,5]</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>3.3068,1.4043,9.6931,11.6694,7.5506,2.4923,8.3482,2.8292,4.3846,12.8430</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:16:25</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.6020392985818407</v>
+      </c>
+      <c r="F48" t="n">
+        <v>92.25952673632452</v>
+      </c>
+      <c r="G48" t="n">
+        <v>94.6220036877689</v>
+      </c>
+      <c r="H48" t="n">
+        <v>46</v>
+      </c>
+      <c r="I48" t="n">
+        <v>68.3006</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>1:08.30</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>64.2804</v>
+      </c>
+      <c r="L48" t="n">
+        <v>1.2413</v>
+      </c>
+      <c r="M48" t="n">
+        <v>2.7781</v>
+      </c>
+      <c r="N48" t="n">
+        <v>3271.2612</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>54:31.26</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>5,6,7,9,8,3,4,0,1,2</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>5:52;6:22;7:53;9:17;8:39;3:70;4:10;0:46;1:30;2:54</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>5:[3,4,5,6,7];6:[2,3];7:[0,1,2,6,7];9:[7];8:[0,1,7];3:[0,1,2,3,5,6,7];4:[2];0:[0,1,2,3];1:[5,6,7];2:[1,2,3,4,5]</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>c5:bw=52,experts=[3,4,5,6,7]; c6:bw=22,experts=[2,3]; c7:bw=53,experts=[0,1,2,6,7]; c9:bw=17,experts=[7]; c8:bw=39,experts=[0,1,7]; c3:bw=70,experts=[0,1,2,3,5,6,7]; c4:bw=10,experts=[2]; c0:bw=46,experts=[0,1,2,3]; c1:bw=30,experts=[5,6,7]; c2:bw=54,experts=[1,2,3,4,5]</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>2.5136,9.6785,12.9526,3.2720,2.8261,1.4084,7.5528,4.4025,11.4097,8.2642</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:17:34</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.6041483666353809</v>
+      </c>
+      <c r="F49" t="n">
+        <v>93.80762138905962</v>
+      </c>
+      <c r="G49" t="n">
+        <v>94.6220036877689</v>
+      </c>
+      <c r="H49" t="n">
+        <v>46</v>
+      </c>
+      <c r="I49" t="n">
+        <v>68.8479</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>1:08.85</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>64.8078</v>
+      </c>
+      <c r="L49" t="n">
+        <v>1.3095</v>
+      </c>
+      <c r="M49" t="n">
+        <v>2.7288</v>
+      </c>
+      <c r="N49" t="n">
+        <v>3340.1353</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>55:40.14</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>1,8,4,2,9,6,5,7,0,3</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>1:50;8:50;4:67;2:57;9:52;6:45;5:55;7:62;0:16;3:18</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>1:[0,1,2,3,4];8:[2,3,4,5,6];4:[0,3,4,5,6,7];2:[0,1,2,6,7];9:[0,1,2,3,4];6:[4,5,6,7];5:[0,1,2,3,4];7:[0,3,4,5,6,7];0:[4];3:[4]</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>c1:bw=50,experts=[0,1,2,3,4]; c8:bw=50,experts=[2,3,4,5,6]; c4:bw=67,experts=[0,3,4,5,6,7]; c2:bw=57,experts=[0,1,2,6,7]; c9:bw=52,experts=[0,1,2,3,4]; c6:bw=45,experts=[4,5,6,7]; c5:bw=55,experts=[0,1,2,3,4]; c7:bw=62,experts=[0,3,4,5,6,7]; c0:bw=16,experts=[4]; c3:bw=18,experts=[4]</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>11.8099,2.8516,7.5867,8.2912,3.2859,9.7140,2.5047,12.9532,4.3815,1.4290</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:18:44</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.6021782362393792</v>
+      </c>
+      <c r="F50" t="n">
+        <v>90.19668100799016</v>
+      </c>
+      <c r="G50" t="n">
+        <v>94.6220036877689</v>
+      </c>
+      <c r="H50" t="n">
+        <v>46</v>
+      </c>
+      <c r="I50" t="n">
+        <v>69.8086</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>1:09.81</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>65.7831</v>
+      </c>
+      <c r="L50" t="n">
+        <v>1.257</v>
+      </c>
+      <c r="M50" t="n">
+        <v>2.7677</v>
+      </c>
+      <c r="N50" t="n">
+        <v>3409.9691</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>56:49.97</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>4,3,8,0,2,5,6,7,9,1</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>4:48;3:32;8:26;0:20;2:58;5:56;6:13;7:44;9:53;1:54</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>4:[1,2,3,4];3:[5,6,7];8:[0,7];0:[5,6];2:[3,4,5,6,7];5:[0,1,5,6,7];6:[0];7:[1,2,3,4];9:[0,1,5,6,7];1:[0,1,5,6,7]</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>c4:bw=48,experts=[1,2,3,4]; c3:bw=32,experts=[5,6,7]; c8:bw=26,experts=[0,7]; c0:bw=20,experts=[5,6]; c2:bw=58,experts=[3,4,5,6,7]; c5:bw=56,experts=[0,1,5,6,7]; c6:bw=13,experts=[0]; c7:bw=44,experts=[1,2,3,4]; c9:bw=53,experts=[0,1,5,6,7]; c1:bw=54,experts=[0,1,5,6,7]</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>7.6246,1.4410,2.8598,4.5639,8.6491,2.6380,9.6282,13.5303,3.4394,11.4088</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:19:53</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.6034595471808925</v>
+      </c>
+      <c r="F51" t="n">
+        <v>94.98693915181315</v>
+      </c>
+      <c r="G51" t="n">
+        <v>94.98693915181315</v>
+      </c>
+      <c r="H51" t="n">
+        <v>50</v>
+      </c>
+      <c r="I51" t="n">
+        <v>68.7657</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>1:08.77</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
+        <v>64.7603</v>
+      </c>
+      <c r="L51" t="n">
+        <v>1.254</v>
+      </c>
+      <c r="M51" t="n">
+        <v>2.7505</v>
+      </c>
+      <c r="N51" t="n">
+        <v>3478.7589</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>57:58.76</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>8,4,7,6,2,1,3,0,9,5</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>8:32;4:10;7:34;6:68;2:63;1:64;3:39;0:29;9:27;5:31</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>8:[1,2,3];4:[5];7:[5,6,7];6:[1,2,3,4,5,6];2:[0,1,2,3,4,5];1:[2,3,4,5,6,7];3:[0,1,2];0:[0,7];9:[2,3];5:[2,3,4]</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>c8:bw=32,experts=[1,2,3]; c4:bw=10,experts=[5]; c7:bw=34,experts=[5,6,7]; c6:bw=68,experts=[1,2,3,4,5,6]; c2:bw=63,experts=[0,1,2,3,4,5]; c1:bw=64,experts=[2,3,4,5,6,7]; c3:bw=39,experts=[0,1,2]; c0:bw=29,experts=[0,7]; c9:bw=27,experts=[2,3]; c5:bw=31,experts=[2,3,4]</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>2.9117,7.5919,12.8459,9.6392,8.2556,11.9325,1.3989,4.3699,3.2660,2.5487</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:21:01</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.5997635087200689</v>
+      </c>
+      <c r="F52" t="n">
+        <v>92.3478795328826</v>
+      </c>
+      <c r="G52" t="n">
+        <v>94.98693915181315</v>
+      </c>
+      <c r="H52" t="n">
+        <v>50</v>
+      </c>
+      <c r="I52" t="n">
+        <v>68.1203</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>1:08.12</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>64.1562</v>
+      </c>
+      <c r="L52" t="n">
+        <v>1.1992</v>
+      </c>
+      <c r="M52" t="n">
+        <v>2.7642</v>
+      </c>
+      <c r="N52" t="n">
+        <v>3546.9035</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>59:06.90</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>5,0,1,2,8,6,9,3,4,7</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>5:47;0:53;1:21;2:20;8:46;6:52;9:18;3:55;4:11;7:27</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>5:[0,5,6,7];0:[1,2,3,4,5];1:[0,1];2:[6,7];8:[4,5,6,7];6:[0,1,2,3,7];9:[4];3:[3,4,5,6,7];4:[6];7:[0,1]</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>c5:bw=47,experts=[0,5,6,7]; c0:bw=53,experts=[1,2,3,4,5]; c1:bw=21,experts=[0,1]; c2:bw=20,experts=[6,7]; c8:bw=46,experts=[4,5,6,7]; c6:bw=52,experts=[0,1,2,3,7]; c9:bw=18,experts=[4]; c3:bw=55,experts=[3,4,5,6,7]; c4:bw=11,experts=[6]; c7:bw=27,experts=[0,1]</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>2.5858,4.4119,11.4283,8.2376,2.8357,9.6177,3.2569,1.3850,7.5110,12.8863</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:22:09</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.6010600230649126</v>
+      </c>
+      <c r="F53" t="n">
+        <v>94.93700061462815</v>
+      </c>
+      <c r="G53" t="n">
+        <v>94.98693915181315</v>
+      </c>
+      <c r="H53" t="n">
+        <v>50</v>
+      </c>
+      <c r="I53" t="n">
+        <v>68.3699</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>1:08.37</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
+        <v>64.3682</v>
+      </c>
+      <c r="L53" t="n">
+        <v>1.2203</v>
+      </c>
+      <c r="M53" t="n">
+        <v>2.7805</v>
+      </c>
+      <c r="N53" t="n">
+        <v>3615.298</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>1:00:15.30</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>0,8,5,7,1,4,9,6,2,3</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>0:46;8:18;5:24;7:34;1:40;4:33;9:31;6:51;2:29;3:43</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>0:[0,1,6,7];8:[0];5:[1,2];7:[2,3,4];1:[2,3,4,5];4:[0,1,7];9:[5,6,7];6:[0,4,5,6,7];2:[0,1];3:[0,1,2,3]</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>c0:bw=46,experts=[0,1,6,7]; c8:bw=18,experts=[0]; c5:bw=24,experts=[1,2]; c7:bw=34,experts=[2,3,4]; c1:bw=40,experts=[2,3,4,5]; c4:bw=33,experts=[0,1,7]; c9:bw=31,experts=[5,6,7]; c6:bw=51,experts=[0,4,5,6,7]; c2:bw=29,experts=[0,1]; c3:bw=43,experts=[0,1,2,3]</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>4.4285,2.8566,2.5003,12.9337,11.5372,7.5533,3.2709,9.6222,8.2369,1.4286</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:23:18</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.598815773708151</v>
+      </c>
+      <c r="F54" t="n">
+        <v>92.51306084818685</v>
+      </c>
+      <c r="G54" t="n">
+        <v>94.98693915181315</v>
+      </c>
+      <c r="H54" t="n">
+        <v>50</v>
+      </c>
+      <c r="I54" t="n">
+        <v>68.73860000000001</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>1:08.74</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
+        <v>64.6542</v>
+      </c>
+      <c r="L54" t="n">
+        <v>1.2776</v>
+      </c>
+      <c r="M54" t="n">
+        <v>2.806</v>
+      </c>
+      <c r="N54" t="n">
+        <v>3684.0623</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>1:01:24.06</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>8,4,5,1,3,9,6,7,0,2</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>8:22;4:28;5:44;1:59;3:47;9:61;6:36;7:44;0:39;2:51</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>8:[1,2];4:[2,3];5:[3,4,5,6];1:[0,1,2,6,7];3:[4,5,6,7];9:[0,1,2,3,4,5];6:[1,2,3];7:[0,5,6,7];0:[2,3,4];2:[2,3,4,5,6]</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>c8:bw=22,experts=[1,2]; c4:bw=28,experts=[2,3]; c5:bw=44,experts=[3,4,5,6]; c1:bw=59,experts=[0,1,2,6,7]; c3:bw=47,experts=[4,5,6,7]; c9:bw=61,experts=[0,1,2,3,4,5]; c6:bw=36,experts=[1,2,3]; c7:bw=44,experts=[0,5,6,7]; c0:bw=39,experts=[2,3,4]; c2:bw=51,experts=[2,3,4,5,6]</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>2.8684,7.6465,2.5064,11.5113,1.3926,3.2889,9.6254,12.9217,4.3943,8.4988</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:24:27</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.599122314686341</v>
+      </c>
+      <c r="F55" t="n">
+        <v>94.24938537185002</v>
+      </c>
+      <c r="G55" t="n">
+        <v>94.98693915181315</v>
+      </c>
+      <c r="H55" t="n">
+        <v>50</v>
+      </c>
+      <c r="I55" t="n">
+        <v>68.3783</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>1:08.38</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
+        <v>64.2865</v>
+      </c>
+      <c r="L55" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M55" t="n">
+        <v>2.8009</v>
+      </c>
+      <c r="N55" t="n">
+        <v>3752.4692</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>1:02:32.47</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>2,1,8,7,3,0,6,5,9,4</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>2:10;1:53;8:55;7:61;3:30;0:37;6:54;5:10;9:50;4:32</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>2:[7];1:[3,4,5,6,7];8:[3,4,5,6,7];7:[1,2,3,4,5,6];3:[0,1,2];0:[5,6,7];6:[0,4,5,6,7];5:[7];9:[0,1,2,6,7];4:[4,5,6]</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>c2:bw=10,experts=[7]; c1:bw=53,experts=[3,4,5,6,7]; c8:bw=55,experts=[3,4,5,6,7]; c7:bw=61,experts=[1,2,3,4,5,6]; c3:bw=30,experts=[0,1,2]; c0:bw=37,experts=[5,6,7]; c6:bw=54,experts=[0,4,5,6,7]; c5:bw=10,experts=[7]; c9:bw=50,experts=[0,1,2,6,7]; c4:bw=32,experts=[4,5,6]</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>8.2942,11.5280,2.8600,12.9127,1.4049,4.3678,9.6259,2.4831,3.2825,7.5275</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:25:35</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.599288069077013</v>
+      </c>
+      <c r="F56" t="n">
+        <v>92.84726490473264</v>
+      </c>
+      <c r="G56" t="n">
+        <v>94.98693915181315</v>
+      </c>
+      <c r="H56" t="n">
+        <v>50</v>
+      </c>
+      <c r="I56" t="n">
+        <v>68.4752</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>1:08.48</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>64.45350000000001</v>
+      </c>
+      <c r="L56" t="n">
+        <v>1.3139</v>
+      </c>
+      <c r="M56" t="n">
+        <v>2.707</v>
+      </c>
+      <c r="N56" t="n">
+        <v>3820.9723</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>1:03:40.97</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>7,2,4,3,8,5,1,6,0,9</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>7:54;2:41;4:14;3:52;8:14;5:53;1:60;6:42;0:27;9:62</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>7:[0,1,2,3,7];2:[0,1,2,3];4:[7];3:[3,4,5,6,7];8:[0];5:[0,1,2,3,4];1:[0,1,2,3,4,5];6:[1,2,3,4];0:[0,1];9:[0,3,4,5,6,7]</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>c7:bw=54,experts=[0,1,2,3,7]; c2:bw=41,experts=[0,1,2,3]; c4:bw=14,experts=[7]; c3:bw=52,experts=[3,4,5,6,7]; c8:bw=14,experts=[0]; c5:bw=53,experts=[0,1,2,3,4]; c1:bw=60,experts=[0,1,2,3,4,5]; c6:bw=42,experts=[1,2,3,4]; c0:bw=27,experts=[0,1]; c9:bw=62,experts=[0,3,4,5,6,7]</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>13.0064,8.3637,7.6074,1.4161,2.8619,2.5106,11.4590,9.6028,4.3584,3.2673</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:26:43</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.5943872774844028</v>
+      </c>
+      <c r="F57" t="n">
+        <v>95.08681622618316</v>
+      </c>
+      <c r="G57" t="n">
+        <v>95.08681622618316</v>
+      </c>
+      <c r="H57" t="n">
+        <v>56</v>
+      </c>
+      <c r="I57" t="n">
+        <v>68.1537</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>1:08.15</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>64.2169</v>
+      </c>
+      <c r="L57" t="n">
+        <v>1.2127</v>
+      </c>
+      <c r="M57" t="n">
+        <v>2.7233</v>
+      </c>
+      <c r="N57" t="n">
+        <v>3889.1538</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>1:04:49.15</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>9,1,3,2,5,4,8,7,6,0</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>9:52;1:56;3:10;2:53;5:31;4:10;8:13;7:18;6:23;0:70</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>9:[1,2,3,4,5];1:[0,1,2,6,7];3:[0];2:[0,4,5,6,7];5:[5,6,7];4:[0];8:[1];7:[4];6:[5,6];0:[0,2,3,4,5,6,7]</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>c9:bw=52,experts=[1,2,3,4,5]; c1:bw=56,experts=[0,1,2,6,7]; c3:bw=10,experts=[0]; c2:bw=53,experts=[0,4,5,6,7]; c5:bw=31,experts=[5,6,7]; c4:bw=10,experts=[0]; c8:bw=13,experts=[1]; c7:bw=18,experts=[4]; c6:bw=23,experts=[5,6]; c0:bw=70,experts=[0,2,3,4,5,6,7]</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>3.2971,11.4156,1.4085,8.2857,2.4783,7.5889,2.8516,12.8832,9.6158,4.3923</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:27:52</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.5939978425741677</v>
+      </c>
+      <c r="F58" t="n">
+        <v>93.14305470190534</v>
+      </c>
+      <c r="G58" t="n">
+        <v>95.08681622618316</v>
+      </c>
+      <c r="H58" t="n">
+        <v>56</v>
+      </c>
+      <c r="I58" t="n">
+        <v>68.44</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>1:08.44</t>
+        </is>
+      </c>
+      <c r="K58" t="n">
+        <v>64.312</v>
+      </c>
+      <c r="L58" t="n">
+        <v>1.357</v>
+      </c>
+      <c r="M58" t="n">
+        <v>2.7701</v>
+      </c>
+      <c r="N58" t="n">
+        <v>3957.6224</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>1:05:57.62</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>3,8,6,1,7,0,5,4,2,9</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>3:64;8:43;6:48;1:49;7:69;0:70;5:44;4:41;2:33;9:19</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>3:[1,2,3,4,5,6];8:[2,3,4,5];6:[0,1,2,7];1:[3,4,5,6];7:[0,1,2,5,6,7];0:[1,2,3,4,5,6,7];5:[0,1,2,3];4:[1,2,3,4];2:[1,2,3];9:[6]</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>c3:bw=64,experts=[1,2,3,4,5,6]; c8:bw=43,experts=[2,3,4,5]; c6:bw=48,experts=[0,1,2,7]; c1:bw=49,experts=[3,4,5,6]; c7:bw=69,experts=[0,1,2,5,6,7]; c0:bw=70,experts=[1,2,3,4,5,6,7]; c5:bw=44,experts=[0,1,2,3]; c4:bw=41,experts=[1,2,3,4]; c2:bw=33,experts=[1,2,3]; c9:bw=19,experts=[6]</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>1.4017,2.8685,9.6801,11.3815,13.0082,4.4060,2.4924,7.5230,8.2543,3.2964</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:29:00</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.5969329045061516</v>
+      </c>
+      <c r="F59" t="n">
+        <v>95.00998770743701</v>
+      </c>
+      <c r="G59" t="n">
+        <v>95.08681622618316</v>
+      </c>
+      <c r="H59" t="n">
+        <v>56</v>
+      </c>
+      <c r="I59" t="n">
+        <v>68.35939999999999</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>1:08.36</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
+        <v>64.3235</v>
+      </c>
+      <c r="L59" t="n">
+        <v>1.2464</v>
+      </c>
+      <c r="M59" t="n">
+        <v>2.7886</v>
+      </c>
+      <c r="N59" t="n">
+        <v>4026.0086</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>1:07:06.01</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>7,2,9,6,5,1,8,4,3,0</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>7:24;2:10;9:57;6:55;5:35;1:30;8:40;4:38;3:61;0:47</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>7:[3,4];2:[4];9:[0,1,2,3,7];6:[3,4,5,6,7];5:[4,5,6];1:[0,1,7];8:[0,1,6,7];4:[5,6,7];3:[0,1,2,3,4,7];0:[0,1,2,3]</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>c7:bw=24,experts=[3,4]; c2:bw=10,experts=[4]; c9:bw=57,experts=[0,1,2,3,7]; c6:bw=55,experts=[3,4,5,6,7]; c5:bw=35,experts=[4,5,6]; c1:bw=30,experts=[0,1,7]; c8:bw=40,experts=[0,1,6,7]; c4:bw=38,experts=[5,6,7]; c3:bw=61,experts=[0,1,2,3,4,7]; c0:bw=47,experts=[0,1,2,3]</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>12.8806,8.2658,3.2965,9.6908,2.4942,11.5018,2.8438,7.5177,1.3982,4.4342</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:30:09</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.5913323548385321</v>
+      </c>
+      <c r="F60" t="n">
+        <v>94.14950829748003</v>
+      </c>
+      <c r="G60" t="n">
+        <v>95.08681622618316</v>
+      </c>
+      <c r="H60" t="n">
+        <v>56</v>
+      </c>
+      <c r="I60" t="n">
+        <v>68.31189999999999</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>1:08.31</t>
+        </is>
+      </c>
+      <c r="K60" t="n">
+        <v>64.2837</v>
+      </c>
+      <c r="L60" t="n">
+        <v>1.2386</v>
+      </c>
+      <c r="M60" t="n">
+        <v>2.7888</v>
+      </c>
+      <c r="N60" t="n">
+        <v>4094.3468</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>1:08:14.35</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>2,8,9,6,1,4,7,5,0,3</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>2:37;8:56;9:28;6:19;1:65;4:26;7:28;5:32;0:52;3:35</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>2:[5,6,7];8:[2,3,4,5,6];9:[4,5];6:[0];1:[2,3,4,5,6,7];4:[0,1];7:[5,6];5:[0,1,7];0:[0,4,5,6,7];3:[5,6,7]</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>c2:bw=37,experts=[5,6,7]; c8:bw=56,experts=[2,3,4,5,6]; c9:bw=28,experts=[4,5]; c6:bw=19,experts=[0]; c1:bw=65,experts=[2,3,4,5,6,7]; c4:bw=26,experts=[0,1]; c7:bw=28,experts=[5,6]; c5:bw=32,experts=[0,1,7]; c0:bw=52,experts=[0,4,5,6,7]; c3:bw=35,experts=[5,6,7]</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>8.2965,2.8610,3.2850,9.6602,11.4035,7.6019,12.8439,2.5393,4.3947,1.3978</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:31:17</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.5943192861865255</v>
+      </c>
+      <c r="F61" t="n">
+        <v>94.48371235402581</v>
+      </c>
+      <c r="G61" t="n">
+        <v>95.08681622618316</v>
+      </c>
+      <c r="H61" t="n">
+        <v>56</v>
+      </c>
+      <c r="I61" t="n">
+        <v>68.3763</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>1:08.38</t>
+        </is>
+      </c>
+      <c r="K61" t="n">
+        <v>64.3892</v>
+      </c>
+      <c r="L61" t="n">
+        <v>1.2123</v>
+      </c>
+      <c r="M61" t="n">
+        <v>2.7739</v>
+      </c>
+      <c r="N61" t="n">
+        <v>4162.7524</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>1:09:22.75</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>0,7,4,2,5,8,6,9,1,3</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>0:53;7:48;4:30;2:30;5:33;8:24;6:59;9:10;1:54;3:44</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>0:[1,2,3,4,5];7:[0,1,2,7];4:[2,3,4];2:[0,1,2];5:[2,3,4];8:[0,7];6:[1,2,3,4,5];9:[6];1:[0,1,2,3,4];3:[0,1,2,3]</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>c0:bw=53,experts=[1,2,3,4,5]; c7:bw=48,experts=[0,1,2,7]; c4:bw=30,experts=[2,3,4]; c2:bw=30,experts=[0,1,2]; c5:bw=33,experts=[2,3,4]; c8:bw=24,experts=[0,7]; c6:bw=59,experts=[1,2,3,4,5]; c9:bw=10,experts=[6]; c1:bw=54,experts=[0,1,2,3,4]; c3:bw=44,experts=[0,1,2,3]</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>4.4174,13.0189,7.6079,8.2903,2.4660,2.8293,9.6331,3.2746,11.4557,1.3960</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:32:25</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.5946189508661045</v>
+      </c>
+      <c r="F62" t="n">
+        <v>94.25322679778733</v>
+      </c>
+      <c r="G62" t="n">
+        <v>95.08681622618316</v>
+      </c>
+      <c r="H62" t="n">
+        <v>56</v>
+      </c>
+      <c r="I62" t="n">
+        <v>68.1164</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>1:08.12</t>
+        </is>
+      </c>
+      <c r="K62" t="n">
+        <v>64.0304</v>
+      </c>
+      <c r="L62" t="n">
+        <v>1.3058</v>
+      </c>
+      <c r="M62" t="n">
+        <v>2.7794</v>
+      </c>
+      <c r="N62" t="n">
+        <v>4230.8984</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>1:10:30.90</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>5,6,2,9,1,3,8,4,7,0</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>5:49;6:37;2:29;9:38;1:33;3:43;8:55;4:38;7:43;0:60</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>5:[0,5,6,7];6:[0,6,7];2:[3,4];9:[0,1,7];1:[5,6,7];3:[4,5,6,7];8:[1,2,3,4,5];4:[5,6,7];7:[3,4,5,6];0:[0,1,2,3,6,7]</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>c5:bw=49,experts=[0,5,6,7]; c6:bw=37,experts=[0,6,7]; c2:bw=29,experts=[3,4]; c9:bw=38,experts=[0,1,7]; c1:bw=33,experts=[5,6,7]; c3:bw=43,experts=[4,5,6,7]; c8:bw=55,experts=[1,2,3,4,5]; c4:bw=38,experts=[5,6,7]; c7:bw=43,experts=[3,4,5,6]; c0:bw=60,experts=[0,1,2,3,6,7]</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>2.4856,9.6608,8.2750,3.3078,11.3629,1.3949,2.8173,7.4868,12.8461,4.3933</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:33:33</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.5935334340544969</v>
+      </c>
+      <c r="F63" t="n">
+        <v>94.69883220651506</v>
+      </c>
+      <c r="G63" t="n">
+        <v>95.08681622618316</v>
+      </c>
+      <c r="H63" t="n">
+        <v>56</v>
+      </c>
+      <c r="I63" t="n">
+        <v>68.2984</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>1:08.30</t>
+        </is>
+      </c>
+      <c r="K63" t="n">
+        <v>64.23309999999999</v>
+      </c>
+      <c r="L63" t="n">
+        <v>1.313</v>
+      </c>
+      <c r="M63" t="n">
+        <v>2.7515</v>
+      </c>
+      <c r="N63" t="n">
+        <v>4299.2256</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>1:11:39.23</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>8,6,9,4,5,0,3,2,1,7</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>8:13;6:62;9:16;4:60;5:67;0:28;3:53;2:42;1:75;7:44</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>8:[6];6:[1,2,3,4,5,6];9:[2];4:[0,1,2,3,4,5];5:[1,2,3,4,5,6];0:[4,5];3:[0,1,2,3,4];2:[0,5,6,7];1:[0,1,2,3,4,5,6];7:[0,1,2,7]</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>c8:bw=13,experts=[6]; c6:bw=62,experts=[1,2,3,4,5,6]; c9:bw=16,experts=[2]; c4:bw=60,experts=[0,1,2,3,4,5]; c5:bw=67,experts=[1,2,3,4,5,6]; c0:bw=28,experts=[4,5]; c3:bw=53,experts=[0,1,2,3,4]; c2:bw=42,experts=[0,5,6,7]; c1:bw=75,experts=[0,1,2,3,4,5,6]; c7:bw=44,experts=[0,1,2,7]</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>2.8339,9.6645,3.2796,7.5987,2.4890,4.3814,1.3973,8.2211,11.4496,12.9179</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:34:42</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.5931086798330434</v>
+      </c>
+      <c r="F64" t="n">
+        <v>94.01889981561156</v>
+      </c>
+      <c r="G64" t="n">
+        <v>95.08681622618316</v>
+      </c>
+      <c r="H64" t="n">
+        <v>56</v>
+      </c>
+      <c r="I64" t="n">
+        <v>68.3947</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>1:08.39</t>
+        </is>
+      </c>
+      <c r="K64" t="n">
+        <v>64.29349999999999</v>
+      </c>
+      <c r="L64" t="n">
+        <v>1.3105</v>
+      </c>
+      <c r="M64" t="n">
+        <v>2.7897</v>
+      </c>
+      <c r="N64" t="n">
+        <v>4367.6505</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>1:12:47.65</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>5,9,6,3,8,1,7,0,2,4</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>5:10;9:21;6:34;3:52;8:32;1:50;7:68;0:41;2:28;4:52</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>5:[7];9:[3,4];6:[0,1,7];3:[0,1,5,6,7];8:[0,1,7];1:[0,1,2,3,7];7:[0,3,4,5,6,7];0:[0,1,6,7];2:[1,2];4:[0,1,2,6,7]</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>c5:bw=10,experts=[7]; c9:bw=21,experts=[3,4]; c6:bw=34,experts=[0,1,7]; c3:bw=52,experts=[0,1,5,6,7]; c8:bw=32,experts=[0,1,7]; c1:bw=50,experts=[0,1,2,3,7]; c7:bw=68,experts=[0,3,4,5,6,7]; c0:bw=41,experts=[0,1,6,7]; c2:bw=28,experts=[1,2]; c4:bw=52,experts=[0,1,2,6,7]</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>2.4818,3.2968,9.7076,1.3997,2.8622,11.4593,12.8931,4.3783,8.2337,7.5812</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:35:50</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.5929986749600064</v>
+      </c>
+      <c r="F65" t="n">
+        <v>92.56684081130916</v>
+      </c>
+      <c r="G65" t="n">
+        <v>95.08681622618316</v>
+      </c>
+      <c r="H65" t="n">
+        <v>56</v>
+      </c>
+      <c r="I65" t="n">
+        <v>68.3901</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>1:08.39</t>
+        </is>
+      </c>
+      <c r="K65" t="n">
+        <v>64.4011</v>
+      </c>
+      <c r="L65" t="n">
+        <v>1.2709</v>
+      </c>
+      <c r="M65" t="n">
+        <v>2.7173</v>
+      </c>
+      <c r="N65" t="n">
+        <v>4436.0683</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>1:13:56.07</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>6,4,5,3,7,0,8,9,2,1</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>6:50;4:38;5:24;3:38;7:34;0:32;8:53;9:59;2:56;1:28</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>6:[2,3,4,5,6];4:[3,4,5];5:[0,1];3:[2,3,4];7:[1,2,3];0:[2,3,4];8:[2,3,4,5,6];9:[0,1,5,6,7];2:[3,4,5,6,7];1:[4,5]</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>c6:bw=50,experts=[2,3,4,5,6]; c4:bw=38,experts=[3,4,5]; c5:bw=24,experts=[0,1]; c3:bw=38,experts=[2,3,4]; c7:bw=34,experts=[1,2,3]; c0:bw=32,experts=[2,3,4]; c8:bw=53,experts=[2,3,4,5,6]; c9:bw=59,experts=[0,1,5,6,7]; c2:bw=56,experts=[3,4,5,6,7]; c1:bw=28,experts=[4,5]</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>9.8189,7.5893,2.5421,1.4072,12.9431,4.4023,2.8550,3.2858,8.2182,11.3392</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:36:59</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.5901461915469564</v>
+      </c>
+      <c r="F66" t="n">
+        <v>93.70390288875231</v>
+      </c>
+      <c r="G66" t="n">
+        <v>95.08681622618316</v>
+      </c>
+      <c r="H66" t="n">
+        <v>56</v>
+      </c>
+      <c r="I66" t="n">
+        <v>68.2854</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>1:08.29</t>
+        </is>
+      </c>
+      <c r="K66" t="n">
+        <v>64.3103</v>
+      </c>
+      <c r="L66" t="n">
+        <v>1.265</v>
+      </c>
+      <c r="M66" t="n">
+        <v>2.7093</v>
+      </c>
+      <c r="N66" t="n">
+        <v>4504.3834</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>1:15:04.38</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>7,5,4,6,8,3,0,2,1,9</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>7:10;5:29;4:57;6:50;8:66;3:42;0:41;2:28;1:58;9:47</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>7:[4];5:[2,3];4:[0,1,2,6,7];6:[0,1,2,3,7];8:[0,1,2,3,4,7];3:[0,5,6,7];0:[0,5,6,7];2:[0,1];1:[0,1,2,6,7];9:[2,3,4,5]</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>c7:bw=10,experts=[4]; c5:bw=29,experts=[2,3]; c4:bw=57,experts=[0,1,2,6,7]; c6:bw=50,experts=[0,1,2,3,7]; c8:bw=66,experts=[0,1,2,3,4,7]; c3:bw=42,experts=[0,5,6,7]; c0:bw=41,experts=[0,5,6,7]; c2:bw=28,experts=[0,1]; c1:bw=58,experts=[0,1,2,6,7]; c9:bw=47,experts=[2,3,4,5]</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>12.9454,2.5030,7.6287,9.7094,2.8505,1.3978,4.3765,8.2315,11.3948,3.2726</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:38:07</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.5886777533760237</v>
+      </c>
+      <c r="F67" t="n">
+        <v>94.11109403810694</v>
+      </c>
+      <c r="G67" t="n">
+        <v>95.08681622618316</v>
+      </c>
+      <c r="H67" t="n">
+        <v>56</v>
+      </c>
+      <c r="I67" t="n">
+        <v>68.2978</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>1:08.30</t>
+        </is>
+      </c>
+      <c r="K67" t="n">
+        <v>64.2735</v>
+      </c>
+      <c r="L67" t="n">
+        <v>1.2883</v>
+      </c>
+      <c r="M67" t="n">
+        <v>2.7352</v>
+      </c>
+      <c r="N67" t="n">
+        <v>4572.7101</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>1:16:12.71</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>2,5,1,8,9,6,4,0,3,7</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>2:41;5:17;1:54;8:24;9:31;6:30;4:41;0:38;3:66;7:50</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>2:[2,3,4,5];5:[4];1:[3,4,5,6,7];8:[5,6];9:[0,6,7];6:[4,5,6];4:[3,4,5,6];0:[1,2,3];3:[1,2,3,4,5,6];7:[0,1,5,6,7]</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>c2:bw=41,experts=[2,3,4,5]; c5:bw=17,experts=[4]; c1:bw=54,experts=[3,4,5,6,7]; c8:bw=24,experts=[5,6]; c9:bw=31,experts=[0,6,7]; c6:bw=30,experts=[4,5,6]; c4:bw=41,experts=[3,4,5,6]; c0:bw=38,experts=[1,2,3]; c3:bw=66,experts=[1,2,3,4,5,6]; c7:bw=50,experts=[0,1,5,6,7]</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>8.2884,2.5101,11.5753,2.8402,3.2949,9.6118,7.5221,4.3791,1.4048,12.8468</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:39:15</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.5891391553996239</v>
+      </c>
+      <c r="F68" t="n">
+        <v>93.08543331284572</v>
+      </c>
+      <c r="G68" t="n">
+        <v>95.08681622618316</v>
+      </c>
+      <c r="H68" t="n">
+        <v>56</v>
+      </c>
+      <c r="I68" t="n">
+        <v>68.4051</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>1:08.41</t>
+        </is>
+      </c>
+      <c r="K68" t="n">
+        <v>64.3488</v>
+      </c>
+      <c r="L68" t="n">
+        <v>1.2537</v>
+      </c>
+      <c r="M68" t="n">
+        <v>2.8017</v>
+      </c>
+      <c r="N68" t="n">
+        <v>4641.1432</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>1:17:21.14</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>4,5,1,3,6,0,2,9,7,8</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>4:51;5:48;1:36;3:25;6:53;0:32;2:43;9:60;7:59;8:10</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>4:[0,1,2,3,7];5:[0,5,6,7];1:[0,1,2];3:[0,7];6:[0,1,2,3,7];0:[4,5,6];2:[0,1,6,7];9:[1,2,3,4,5,6];7:[2,3,4,5,6];8:[7]</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>c4:bw=51,experts=[0,1,2,3,7]; c5:bw=48,experts=[0,5,6,7]; c1:bw=36,experts=[0,1,2]; c3:bw=25,experts=[0,7]; c6:bw=53,experts=[0,1,2,3,7]; c0:bw=32,experts=[4,5,6]; c2:bw=43,experts=[0,1,6,7]; c9:bw=60,experts=[1,2,3,4,5,6]; c7:bw=59,experts=[2,3,4,5,6]; c8:bw=10,experts=[7]</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>7.5717,2.5070,11.5282,1.4029,9.7132,4.3823,8.2629,3.2765,12.8914,2.8127</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:40:24</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.5874761944523518</v>
+      </c>
+      <c r="F69" t="n">
+        <v>94.58743085433314</v>
+      </c>
+      <c r="G69" t="n">
+        <v>95.08681622618316</v>
+      </c>
+      <c r="H69" t="n">
+        <v>56</v>
+      </c>
+      <c r="I69" t="n">
+        <v>68.1699</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>1:08.17</t>
+        </is>
+      </c>
+      <c r="K69" t="n">
+        <v>64.1575</v>
+      </c>
+      <c r="L69" t="n">
+        <v>1.2176</v>
+      </c>
+      <c r="M69" t="n">
+        <v>2.794</v>
+      </c>
+      <c r="N69" t="n">
+        <v>4709.3417</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>1:18:29.34</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>1,8,2,0,3,4,5,9,7,6</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>1:42;8:31;2:58;0:30;3:26;4:49;5:45;9:15;7:28;6:32</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>1:[3,4,5,6];8:[0,1,2];2:[2,3,4,5,6];0:[0,1,7];3:[1,2];4:[4,5,6,7];5:[1,2,3,4];9:[7];7:[0,7];6:[4,5,6]</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>c1:bw=42,experts=[3,4,5,6]; c8:bw=31,experts=[0,1,2]; c2:bw=58,experts=[2,3,4,5,6]; c0:bw=30,experts=[0,1,7]; c3:bw=26,experts=[1,2]; c4:bw=49,experts=[4,5,6,7]; c5:bw=45,experts=[1,2,3,4]; c9:bw=15,experts=[7]; c7:bw=28,experts=[0,7]; c6:bw=32,experts=[4,5,6]</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>11.3856,2.8599,8.3054,4.4685,1.3998,7.5395,2.4792,3.2615,12.8384,9.6197</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:41:32</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.5868445746104008</v>
+      </c>
+      <c r="F70" t="n">
+        <v>93.38890596189306</v>
+      </c>
+      <c r="G70" t="n">
+        <v>95.08681622618316</v>
+      </c>
+      <c r="H70" t="n">
+        <v>56</v>
+      </c>
+      <c r="I70" t="n">
+        <v>68.25360000000001</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>1:08.25</t>
+        </is>
+      </c>
+      <c r="K70" t="n">
+        <v>64.21469999999999</v>
+      </c>
+      <c r="L70" t="n">
+        <v>1.2628</v>
+      </c>
+      <c r="M70" t="n">
+        <v>2.7753</v>
+      </c>
+      <c r="N70" t="n">
+        <v>4777.6245</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>1:19:37.62</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>3,7,1,4,9,5,0,2,8,6</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>3:41;7:58;1:31;4:41;9:35;5:39;0:52;2:66;8:42;6:26</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>3:[3,4,5,6];7:[1,2,3,4,5];1:[0,1,7];4:[0,1,2,3];9:[0,1,2];5:[5,6,7];0:[2,3,4,5,6];2:[0,1,2,3,4,7];8:[3,4,5,6];6:[0,7]</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>c3:bw=41,experts=[3,4,5,6]; c7:bw=58,experts=[1,2,3,4,5]; c1:bw=31,experts=[0,1,7]; c4:bw=41,experts=[0,1,2,3]; c9:bw=35,experts=[0,1,2]; c5:bw=39,experts=[5,6,7]; c0:bw=52,experts=[2,3,4,5,6]; c2:bw=66,experts=[0,1,2,3,4,7]; c8:bw=42,experts=[3,4,5,6]; c6:bw=26,experts=[0,7]</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>1.3806,12.9354,11.4423,7.6212,3.2948,2.4932,4.3834,8.2427,2.8167,9.6045</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:42:40</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.5857265732337299</v>
+      </c>
+      <c r="F71" t="n">
+        <v>95.29041180086048</v>
+      </c>
+      <c r="G71" t="n">
+        <v>95.29041180086048</v>
+      </c>
+      <c r="H71" t="n">
+        <v>70</v>
+      </c>
+      <c r="I71" t="n">
+        <v>68.197</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>1:08.20</t>
+        </is>
+      </c>
+      <c r="K71" t="n">
+        <v>64.20059999999999</v>
+      </c>
+      <c r="L71" t="n">
+        <v>1.2099</v>
+      </c>
+      <c r="M71" t="n">
+        <v>2.7858</v>
+      </c>
+      <c r="N71" t="n">
+        <v>4845.8504</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>1:20:45.85</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>1,9,7,3,0,6,2,4,5,8</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>1:24;9:10;7:28;3:32;0:30;6:26;2:55;4:58;5:23;8:48</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>1:[2,3];9:[3];7:[6,7];3:[0,1,7];0:[0,1,7];6:[1,2];2:[0,1,5,6,7];4:[0,4,5,6,7];5:[0,1];8:[0,1,2,7]</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>c1:bw=24,experts=[2,3]; c9:bw=10,experts=[3]; c7:bw=28,experts=[6,7]; c3:bw=32,experts=[0,1,7]; c0:bw=30,experts=[0,1,7]; c6:bw=26,experts=[1,2]; c2:bw=55,experts=[0,1,5,6,7]; c4:bw=58,experts=[0,4,5,6,7]; c5:bw=23,experts=[0,1]; c8:bw=48,experts=[0,1,2,7]</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>11.4570,3.2740,12.9010,1.3964,4.4065,9.6762,8.2447,7.5366,2.4712,2.8370</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:43:48</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.5863565603368295</v>
+      </c>
+      <c r="F72" t="n">
+        <v>93.41579594345421</v>
+      </c>
+      <c r="G72" t="n">
+        <v>95.29041180086048</v>
+      </c>
+      <c r="H72" t="n">
+        <v>70</v>
+      </c>
+      <c r="I72" t="n">
+        <v>68.2693</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>1:08.27</t>
+        </is>
+      </c>
+      <c r="K72" t="n">
+        <v>64.1887</v>
+      </c>
+      <c r="L72" t="n">
+        <v>1.2901</v>
+      </c>
+      <c r="M72" t="n">
+        <v>2.7897</v>
+      </c>
+      <c r="N72" t="n">
+        <v>4914.1491</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>1:21:54.15</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>4,0,1,9,7,5,3,6,8,2</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>4:42;0:16;1:52;9:40;7:20;5:33;3:62;6:50;8:39;2:61</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>4:[1,2,3,4];0:[2];1:[0,4,5,6,7];9:[4,5,6,7];7:[0,1];5:[2,3,4];3:[2,3,4,5,6,7];6:[3,4,5,6,7];8:[3,4,5];2:[2,3,4,5,6,7]</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>c4:bw=42,experts=[1,2,3,4]; c0:bw=16,experts=[2]; c1:bw=52,experts=[0,4,5,6,7]; c9:bw=40,experts=[4,5,6,7]; c7:bw=20,experts=[0,1]; c5:bw=33,experts=[2,3,4]; c3:bw=62,experts=[2,3,4,5,6,7]; c6:bw=50,experts=[3,4,5,6,7]; c8:bw=39,experts=[3,4,5]; c2:bw=61,experts=[2,3,4,5,6,7]</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>7.5881,4.4310,11.4209,3.2912,12.9358,2.4982,1.3962,9.5925,2.8195,8.2154</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:44:57</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.5867307466103479</v>
+      </c>
+      <c r="F73" t="n">
+        <v>94.49523663183774</v>
+      </c>
+      <c r="G73" t="n">
+        <v>95.29041180086048</v>
+      </c>
+      <c r="H73" t="n">
+        <v>70</v>
+      </c>
+      <c r="I73" t="n">
+        <v>68.3661</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>1:08.37</t>
+        </is>
+      </c>
+      <c r="K73" t="n">
+        <v>64.38890000000001</v>
+      </c>
+      <c r="L73" t="n">
+        <v>1.2027</v>
+      </c>
+      <c r="M73" t="n">
+        <v>2.7737</v>
+      </c>
+      <c r="N73" t="n">
+        <v>4982.5452</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>1:23:02.55</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>8,1,5,7,6,0,3,2,9,4</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>8:30;1:39;5:43;7:48;6:19;0:52;3:23;2:23;9:38;4:39</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>8:[0,6,7];1:[1,2,3];5:[0,5,6,7];7:[2,3,4,5];6:[0];0:[3,4,5,6,7];3:[0,1];2:[0,1];9:[0,1,2];4:[5,6,7]</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>c8:bw=30,experts=[0,6,7]; c1:bw=39,experts=[1,2,3]; c5:bw=43,experts=[0,5,6,7]; c7:bw=48,experts=[2,3,4,5]; c6:bw=19,experts=[0]; c0:bw=52,experts=[3,4,5,6,7]; c3:bw=23,experts=[0,1]; c2:bw=23,experts=[0,1]; c9:bw=38,experts=[0,1,2]; c4:bw=39,experts=[5,6,7]</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>2.8379,11.4927,2.4926,12.9603,9.6859,4.4170,1.4170,8.2589,3.2937,7.5330</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:46:05</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.5864933962674672</v>
+      </c>
+      <c r="F74" t="n">
+        <v>94.46066379840197</v>
+      </c>
+      <c r="G74" t="n">
+        <v>95.29041180086048</v>
+      </c>
+      <c r="H74" t="n">
+        <v>70</v>
+      </c>
+      <c r="I74" t="n">
+        <v>68.38809999999999</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>1:08.39</t>
+        </is>
+      </c>
+      <c r="K74" t="n">
+        <v>64.38679999999999</v>
+      </c>
+      <c r="L74" t="n">
+        <v>1.2165</v>
+      </c>
+      <c r="M74" t="n">
+        <v>2.784</v>
+      </c>
+      <c r="N74" t="n">
+        <v>5050.9632</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>1:24:10.96</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>2,8,3,1,5,9,0,7,6,4</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>2:47;8:11;3:40;1:66;5:17;9:52;0:28;7:37;6:20;4:41</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>2:[2,3,4,5];8:[1];3:[2,3,4,5];1:[0,1,4,5,6,7];5:[1];9:[3,4,5,6,7];0:[0,1];7:[0,6,7];6:[1,2];4:[0,1,2,3]</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>c2:bw=47,experts=[2,3,4,5]; c8:bw=11,experts=[1]; c3:bw=40,experts=[2,3,4,5]; c1:bw=66,experts=[0,1,4,5,6,7]; c5:bw=17,experts=[1]; c9:bw=52,experts=[3,4,5,6,7]; c0:bw=28,experts=[0,1]; c7:bw=37,experts=[0,6,7]; c6:bw=20,experts=[1,2]; c4:bw=41,experts=[0,1,2,3]</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>8.2909,2.8585,1.3978,11.4705,2.4669,3.2906,4.3906,12.9072,9.7103,7.6035</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:47:13</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.5859156351885167</v>
+      </c>
+      <c r="F75" t="n">
+        <v>91.93300553165335</v>
+      </c>
+      <c r="G75" t="n">
+        <v>95.29041180086048</v>
+      </c>
+      <c r="H75" t="n">
+        <v>70</v>
+      </c>
+      <c r="I75" t="n">
+        <v>68.1785</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>1:08.18</t>
+        </is>
+      </c>
+      <c r="K75" t="n">
+        <v>64.2067</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.2065</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2.7646</v>
+      </c>
+      <c r="N75" t="n">
+        <v>5119.1724</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>1:25:19.17</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>3,0,1,5,7,8,6,2,4,9</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>3:10;0:40;1:28;5:50;7:65;8:28;6:10;2:10;4:47;9:32</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>3:[6];0:[2,3,4,5];1:[2,3];5:[2,3,4,5,6];7:[1,2,3,4,5,6];8:[2,3];6:[3];2:[6];4:[4,5,6,7];9:[0,1,2]</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>c3:bw=10,experts=[6]; c0:bw=40,experts=[2,3,4,5]; c1:bw=28,experts=[2,3]; c5:bw=50,experts=[2,3,4,5,6]; c7:bw=65,experts=[1,2,3,4,5,6]; c8:bw=28,experts=[2,3]; c6:bw=10,experts=[3]; c2:bw=10,experts=[6]; c4:bw=47,experts=[4,5,6,7]; c9:bw=32,experts=[0,1,2]</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>1.3979,4.4166,11.4280,2.4778,12.9357,2.8370,9.6054,8.2291,7.5816,3.2974</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:48:22</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.5843670780520376</v>
+      </c>
+      <c r="F76" t="n">
+        <v>94.54517516902274</v>
+      </c>
+      <c r="G76" t="n">
+        <v>95.29041180086048</v>
+      </c>
+      <c r="H76" t="n">
+        <v>70</v>
+      </c>
+      <c r="I76" t="n">
+        <v>68.3901</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>1:08.39</t>
+        </is>
+      </c>
+      <c r="K76" t="n">
+        <v>64.2621</v>
+      </c>
+      <c r="L76" t="n">
+        <v>1.3427</v>
+      </c>
+      <c r="M76" t="n">
+        <v>2.7844</v>
+      </c>
+      <c r="N76" t="n">
+        <v>5187.5929</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>1:26:27.59</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>2,9,1,3,7,6,5,4,0,8</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>2:40;9:61;1:54;3:20;7:28;6:56;5:31;4:56;0:60;8:53</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>2:[0,1,2,7];9:[0,3,4,5,6,7];1:[0,4,5,6,7];3:[0,7];7:[0,7];6:[0,4,5,6,7];5:[0,1,7];4:[0,1,2,3,4];0:[0,1,2,3,6,7];8:[0,4,5,6,7]</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>c2:bw=40,experts=[0,1,2,7]; c9:bw=61,experts=[0,3,4,5,6,7]; c1:bw=54,experts=[0,4,5,6,7]; c3:bw=20,experts=[0,7]; c7:bw=28,experts=[0,7]; c6:bw=56,experts=[0,4,5,6,7]; c5:bw=31,experts=[0,1,7]; c4:bw=56,experts=[0,1,2,3,4]; c0:bw=60,experts=[0,1,2,3,6,7]; c8:bw=53,experts=[0,4,5,6,7]</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>8.3432,3.2857,11.4209,1.4327,12.8970,9.6189,2.4627,7.5626,4.3909,2.8474</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:49:30</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.584267288688547</v>
+      </c>
+      <c r="F77" t="n">
+        <v>93.96127842655194</v>
+      </c>
+      <c r="G77" t="n">
+        <v>95.29041180086048</v>
+      </c>
+      <c r="H77" t="n">
+        <v>70</v>
+      </c>
+      <c r="I77" t="n">
+        <v>68.2086</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>1:08.21</t>
+        </is>
+      </c>
+      <c r="K77" t="n">
+        <v>64.1528</v>
+      </c>
+      <c r="L77" t="n">
+        <v>1.2685</v>
+      </c>
+      <c r="M77" t="n">
+        <v>2.7865</v>
+      </c>
+      <c r="N77" t="n">
+        <v>5255.8325</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>1:27:35.83</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>8,5,0,3,2,6,7,4,9,1</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>8:29;5:37;0:31;3:15;2:25;6:23;7:66;4:60;9:57;1:53</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>8:[1,2];5:[2,3,4];0:[4,5,6];3:[1];2:[3,4];6:[1,2];7:[1,2,3,4,5,6];4:[0,1,2,5,6,7];9:[1,2,3,4,5];1:[1,2,3,4,5]</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>c8:bw=29,experts=[1,2]; c5:bw=37,experts=[2,3,4]; c0:bw=31,experts=[4,5,6]; c3:bw=15,experts=[1]; c2:bw=25,experts=[3,4]; c6:bw=23,experts=[1,2]; c7:bw=66,experts=[1,2,3,4,5,6]; c4:bw=60,experts=[0,1,2,5,6,7]; c9:bw=57,experts=[1,2,3,4,5]; c1:bw=53,experts=[1,2,3,4,5]</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>2.8729,2.5027,4.4235,1.3998,8.2442,9.6249,12.8622,7.5645,3.2640,11.3940</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:50:38</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.5849229099092021</v>
+      </c>
+      <c r="F78" t="n">
+        <v>95.42102028272895</v>
+      </c>
+      <c r="G78" t="n">
+        <v>95.42102028272895</v>
+      </c>
+      <c r="H78" t="n">
+        <v>77</v>
+      </c>
+      <c r="I78" t="n">
+        <v>68.2824</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>1:08.28</t>
+        </is>
+      </c>
+      <c r="K78" t="n">
+        <v>64.2323</v>
+      </c>
+      <c r="L78" t="n">
+        <v>1.2586</v>
+      </c>
+      <c r="M78" t="n">
+        <v>2.7907</v>
+      </c>
+      <c r="N78" t="n">
+        <v>5324.1461</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>1:28:44.15</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>9,2,1,8,4,7,6,0,3,5</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>9:29;2:34;1:62;8:10;4:10;7:10;6:57;0:63;3:40;5:59</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>9:[6,7];2:[5,6,7];1:[0,1,2,3,6,7];8:[3];4:[3];7:[7];6:[3,4,5,6,7];0:[0,1,2,3,4,7];3:[2,3,4,5];5:[0,1,5,6,7]</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>c9:bw=29,experts=[6,7]; c2:bw=34,experts=[5,6,7]; c1:bw=62,experts=[0,1,2,3,6,7]; c8:bw=10,experts=[3]; c4:bw=10,experts=[3]; c7:bw=10,experts=[7]; c6:bw=57,experts=[3,4,5,6,7]; c0:bw=63,experts=[0,1,2,3,4,7]; c3:bw=40,experts=[2,3,4,5]; c5:bw=59,experts=[0,1,5,6,7]</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>3.2845,8.2910,11.4835,2.8464,7.5643,12.8796,9.6285,4.3870,1.3884,2.4791</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:51:47</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.5820869281171765</v>
+      </c>
+      <c r="F79" t="n">
+        <v>94.23786109403811</v>
+      </c>
+      <c r="G79" t="n">
+        <v>95.42102028272895</v>
+      </c>
+      <c r="H79" t="n">
+        <v>77</v>
+      </c>
+      <c r="I79" t="n">
+        <v>68.2972</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>1:08.30</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
+        <v>64.2625</v>
+      </c>
+      <c r="L79" t="n">
+        <v>1.2449</v>
+      </c>
+      <c r="M79" t="n">
+        <v>2.789</v>
+      </c>
+      <c r="N79" t="n">
+        <v>5392.4743</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>1:29:52.47</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>0,4,3,7,8,1,9,6,5,2</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>0:26;4:23;3:38;7:36;8:54;1:41;9:31;6:57;5:63;2:34</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>0:[5,6];4:[4,5];3:[0,6,7];7:[0,1,2];8:[0,4,5,6,7];1:[4,5,6,7];9:[0,1,2];6:[0,1,2,3,4];5:[2,3,4,5,6,7];2:[0,1,2]</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>c0:bw=26,experts=[5,6]; c4:bw=23,experts=[4,5]; c3:bw=38,experts=[0,6,7]; c7:bw=36,experts=[0,1,2]; c8:bw=54,experts=[0,4,5,6,7]; c1:bw=41,experts=[4,5,6,7]; c9:bw=31,experts=[0,1,2]; c6:bw=57,experts=[0,1,2,3,4]; c5:bw=63,experts=[2,3,4,5,6,7]; c2:bw=34,experts=[0,1,2]</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>4.4030,7.6159,1.3969,12.9687,2.8253,11.3539,3.3001,9.6685,2.4747,8.2554</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:52:55</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.5821694062499263</v>
+      </c>
+      <c r="F80" t="n">
+        <v>94.53749231714812</v>
+      </c>
+      <c r="G80" t="n">
+        <v>95.42102028272895</v>
+      </c>
+      <c r="H80" t="n">
+        <v>77</v>
+      </c>
+      <c r="I80" t="n">
+        <v>68.2546</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>1:08.25</t>
+        </is>
+      </c>
+      <c r="K80" t="n">
+        <v>64.23220000000001</v>
+      </c>
+      <c r="L80" t="n">
+        <v>1.2303</v>
+      </c>
+      <c r="M80" t="n">
+        <v>2.7913</v>
+      </c>
+      <c r="N80" t="n">
+        <v>5460.76</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>1:31:00.76</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>6,9,0,4,7,8,5,3,1,2</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>6:21;9:10;0:36;4:80;7:46;8:44;5:53;3:26;1:37;2:33</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>6:[5,6];9:[3];0:[0,1,7];4:[0,1,2,3,4,5,6,7];7:[3,4,5,6];8:[1,2,3,4];5:[0,1,2,3,4];3:[1,2];1:[0,1,2];2:[3,4,5]</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>c6:bw=21,experts=[5,6]; c9:bw=10,experts=[3]; c0:bw=36,experts=[0,1,7]; c4:bw=80,experts=[0,1,2,3,4,5,6,7]; c7:bw=46,experts=[3,4,5,6]; c8:bw=44,experts=[1,2,3,4]; c5:bw=53,experts=[0,1,2,3,4]; c3:bw=26,experts=[1,2]; c1:bw=37,experts=[0,1,2]; c2:bw=33,experts=[3,4,5]</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>9.6885,3.3083,4.4024,7.6337,12.8733,2.8346,2.4826,1.3892,11.4176,8.2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:54:03</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0.5819695952821423</v>
+      </c>
+      <c r="F81" t="n">
+        <v>94.41840811309157</v>
+      </c>
+      <c r="G81" t="n">
+        <v>95.42102028272895</v>
+      </c>
+      <c r="H81" t="n">
+        <v>77</v>
+      </c>
+      <c r="I81" t="n">
+        <v>68.4593</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>1:08.46</t>
+        </is>
+      </c>
+      <c r="K81" t="n">
+        <v>64.3289</v>
+      </c>
+      <c r="L81" t="n">
+        <v>1.3204</v>
+      </c>
+      <c r="M81" t="n">
+        <v>2.8091</v>
+      </c>
+      <c r="N81" t="n">
+        <v>5529.2525</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>1:32:09.25</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>5,9,7,1,3,4,2,0,6,8</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>5:65;9:53;7:48;1:31;3:31;4:57;2:44;0:47;6:39;8:51</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>5:[0,1,2,5,6,7];9:[0,4,5,6,7];7:[0,1,2,7];1:[3,4,5];3:[3,4,5];4:[0,1,2,6,7];2:[0,1,6,7];0:[2,3,4,5];6:[0,1,7];8:[0,1,5,6,7]</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>c5:bw=65,experts=[0,1,2,5,6,7]; c9:bw=53,experts=[0,4,5,6,7]; c7:bw=48,experts=[0,1,2,7]; c1:bw=31,experts=[3,4,5]; c3:bw=31,experts=[3,4,5]; c4:bw=57,experts=[0,1,2,6,7]; c2:bw=44,experts=[0,1,6,7]; c0:bw=47,experts=[2,3,4,5]; c6:bw=39,experts=[0,1,7]; c8:bw=51,experts=[0,1,5,6,7]</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>2.4874,3.2912,13.0180,11.4473,1.3965,7.5784,8.2255,4.3915,9.6606,2.8324</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:55:12</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0.5801812103396824</v>
+      </c>
+      <c r="F82" t="n">
+        <v>93.31207744314689</v>
+      </c>
+      <c r="G82" t="n">
+        <v>95.42102028272895</v>
+      </c>
+      <c r="H82" t="n">
+        <v>77</v>
+      </c>
+      <c r="I82" t="n">
+        <v>68.3188</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>1:08.32</t>
+        </is>
+      </c>
+      <c r="K82" t="n">
+        <v>64.2612</v>
+      </c>
+      <c r="L82" t="n">
+        <v>1.2935</v>
+      </c>
+      <c r="M82" t="n">
+        <v>2.7633</v>
+      </c>
+      <c r="N82" t="n">
+        <v>5597.6034</v>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>1:33:17.60</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>6,2,3,1,4,5,9,7,8,0</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>6:51;2:45;3:67;1:49;4:42;5:30;9:26;7:58;8:48;0:50</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>6:[2,3,4,5,6];2:[2,3,4,5];3:[0,1,2,3,6,7];1:[0,1,6,7];4:[3,4,5,6];5:[3,4,5];9:[1,2];7:[3,4,5,6,7];8:[2,3,4,5];0:[0,1,2,6,7]</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>c6:bw=51,experts=[2,3,4,5,6]; c2:bw=45,experts=[2,3,4,5]; c3:bw=67,experts=[0,1,2,3,6,7]; c1:bw=49,experts=[0,1,6,7]; c4:bw=42,experts=[3,4,5,6]; c5:bw=30,experts=[3,4,5]; c9:bw=26,experts=[1,2]; c7:bw=58,experts=[3,4,5,6,7]; c8:bw=48,experts=[2,3,4,5]; c0:bw=50,experts=[0,1,2,6,7]</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>9.6885,8.3136,1.4262,11.4381,7.5562,2.4630,3.2871,12.8115,2.8404,4.4367</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:56:20</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0.5802437740925918</v>
+      </c>
+      <c r="F83" t="n">
+        <v>94.73724646588813</v>
+      </c>
+      <c r="G83" t="n">
+        <v>95.42102028272895</v>
+      </c>
+      <c r="H83" t="n">
+        <v>77</v>
+      </c>
+      <c r="I83" t="n">
+        <v>68.37430000000001</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>1:08.37</t>
+        </is>
+      </c>
+      <c r="K83" t="n">
+        <v>64.35890000000001</v>
+      </c>
+      <c r="L83" t="n">
+        <v>1.3007</v>
+      </c>
+      <c r="M83" t="n">
+        <v>2.7138</v>
+      </c>
+      <c r="N83" t="n">
+        <v>5666.01</v>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>1:34:26.01</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>1,0,6,8,7,3,2,9,5,4</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>1:64;0:30;6:36;8:58;7:40;3:39;2:30;9:56;5:40;4:30</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>1:[2,3,4,5,6,7];0:[3,4,5];6:[0,1,7];8:[0,1,2,6,7];7:[0,1,2,3];3:[4,5,6];2:[0,6,7];9:[3,4,5,6,7];5:[0,1,6,7];4:[0,1,7]</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>c1:bw=64,experts=[2,3,4,5,6,7]; c0:bw=30,experts=[3,4,5]; c6:bw=36,experts=[0,1,7]; c8:bw=58,experts=[0,1,2,6,7]; c7:bw=40,experts=[0,1,2,3]; c3:bw=39,experts=[4,5,6]; c2:bw=30,experts=[0,6,7]; c9:bw=56,experts=[3,4,5,6,7]; c5:bw=40,experts=[0,1,6,7]; c4:bw=30,experts=[0,1,7]</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>11.4854,4.3758,9.7042,2.8527,13.0054,1.4013,8.2229,3.2438,2.5098,7.5575</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:57:28</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0.5808375726230585</v>
+      </c>
+      <c r="F84" t="n">
+        <v>93.11232329440688</v>
+      </c>
+      <c r="G84" t="n">
+        <v>95.42102028272895</v>
+      </c>
+      <c r="H84" t="n">
+        <v>77</v>
+      </c>
+      <c r="I84" t="n">
+        <v>68.27589999999999</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>1:08.28</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
+        <v>64.28319999999999</v>
+      </c>
+      <c r="L84" t="n">
+        <v>1.2321</v>
+      </c>
+      <c r="M84" t="n">
+        <v>2.7597</v>
+      </c>
+      <c r="N84" t="n">
+        <v>5734.3182</v>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>1:35:34.32</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>9,4,2,7,5,0,6,1,8,3</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>9:51;4:10;2:41;7:37;5:10;0:10;6:53;1:63;8:39;3:42</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>9:[0,1,2,3,4];4:[2];2:[1,2,3,4];7:[4,5,6];5:[2];0:[6];6:[2,3,4,5,6];1:[0,1,2,3,4,5];8:[3,4,5];3:[0,1,2,7]</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>c9:bw=51,experts=[0,1,2,3,4]; c4:bw=10,experts=[2]; c2:bw=41,experts=[1,2,3,4]; c7:bw=37,experts=[4,5,6]; c5:bw=10,experts=[2]; c0:bw=10,experts=[6]; c6:bw=53,experts=[2,3,4,5,6]; c1:bw=63,experts=[0,1,2,3,4,5]; c8:bw=39,experts=[3,4,5]; c3:bw=42,experts=[0,1,2,7]</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>3.3075,7.5611,8.2715,12.9777,2.5007,4.3888,9.6526,11.3899,2.8199,1.4135</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:58:37</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0.579073948394472</v>
+      </c>
+      <c r="F85" t="n">
+        <v>94.64121081745544</v>
+      </c>
+      <c r="G85" t="n">
+        <v>95.42102028272895</v>
+      </c>
+      <c r="H85" t="n">
+        <v>77</v>
+      </c>
+      <c r="I85" t="n">
+        <v>68.268</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>1:08.27</t>
+        </is>
+      </c>
+      <c r="K85" t="n">
+        <v>64.2991</v>
+      </c>
+      <c r="L85" t="n">
+        <v>1.1992</v>
+      </c>
+      <c r="M85" t="n">
+        <v>2.7689</v>
+      </c>
+      <c r="N85" t="n">
+        <v>5802.6185</v>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>1:36:42.62</t>
+        </is>
+      </c>
+      <c r="P85" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>8,3,1,6,9,2,7,5,4,0</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>8:67;3:32;1:58;6:10;9:20;2:36;7:47;5:20;4:27;0:10</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>8:[0,1,2,3,6,7];3:[3,4,5];1:[0,1,2,6,7];6:[7];9:[5,6];2:[5,6,7];7:[0,1,2,7];5:[3,4];4:[3,4];0:[7]</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>c8:bw=67,experts=[0,1,2,3,6,7]; c3:bw=32,experts=[3,4,5]; c1:bw=58,experts=[0,1,2,6,7]; c6:bw=10,experts=[7]; c9:bw=20,experts=[5,6]; c2:bw=36,experts=[5,6,7]; c7:bw=47,experts=[0,1,2,7]; c5:bw=20,experts=[3,4]; c4:bw=27,experts=[3,4]; c0:bw=10,experts=[7]</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>2.8541,1.4274,11.5110,9.6512,3.2664,8.2747,12.9775,2.4699,7.5007,4.3660</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:59:45</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0.5802988690412307</v>
+      </c>
+      <c r="F86" t="n">
+        <v>94.58743085433314</v>
+      </c>
+      <c r="G86" t="n">
+        <v>95.42102028272895</v>
+      </c>
+      <c r="H86" t="n">
+        <v>77</v>
+      </c>
+      <c r="I86" t="n">
+        <v>68.2924</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>1:08.29</t>
+        </is>
+      </c>
+      <c r="K86" t="n">
+        <v>64.2136</v>
+      </c>
+      <c r="L86" t="n">
+        <v>1.302</v>
+      </c>
+      <c r="M86" t="n">
+        <v>2.7759</v>
+      </c>
+      <c r="N86" t="n">
+        <v>5871.0191</v>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>1:37:51.02</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>0,2,8,6,1,4,9,3,5,7</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>0:38;2:45;8:70;6:42;1:57;4:42;9:58;3:51;5:12;7:11</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>0:[0,1,2];2:[0,1,2,3];8:[0,1,2,4,5,6,7];6:[0,1,2,3];1:[3,4,5,6,7];4:[0,5,6,7];9:[0,1,2,3,7];3:[0,1,2,6,7];5:[5];7:[3]</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>c0:bw=38,experts=[0,1,2]; c2:bw=45,experts=[0,1,2,3]; c8:bw=70,experts=[0,1,2,4,5,6,7]; c6:bw=42,experts=[0,1,2,3]; c1:bw=57,experts=[3,4,5,6,7]; c4:bw=42,experts=[0,5,6,7]; c9:bw=58,experts=[0,1,2,3,7]; c3:bw=51,experts=[0,1,2,6,7]; c5:bw=12,experts=[5]; c7:bw=11,experts=[3]</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>4.4137,8.3226,2.8492,9.6649,11.3331,7.5746,3.2891,1.4233,2.4730,12.8702</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:00:53</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0.5798433101489885</v>
+      </c>
+      <c r="F87" t="n">
+        <v>95.14827904118009</v>
+      </c>
+      <c r="G87" t="n">
+        <v>95.42102028272895</v>
+      </c>
+      <c r="H87" t="n">
+        <v>77</v>
+      </c>
+      <c r="I87" t="n">
+        <v>68.23139999999999</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>1:08.23</t>
+        </is>
+      </c>
+      <c r="K87" t="n">
+        <v>64.20489999999999</v>
+      </c>
+      <c r="L87" t="n">
+        <v>1.2509</v>
+      </c>
+      <c r="M87" t="n">
+        <v>2.7748</v>
+      </c>
+      <c r="N87" t="n">
+        <v>5939.2838</v>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>1:38:59.28</t>
+        </is>
+      </c>
+      <c r="P87" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>5,8,2,6,0,4,7,3,1,9</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>5:47;8:28;2:24;6:55;0:30;4:18;7:44;3:28;1:72;9:43</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>5:[0,1,6,7];8:[3,4];2:[4,5];6:[0,4,5,6,7];0:[3,4,5];4:[1];7:[4,5,6,7];3:[3,4];1:[0,1,2,3,4,5,6];9:[4,5,6,7]</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>c5:bw=47,experts=[0,1,6,7]; c8:bw=28,experts=[3,4]; c2:bw=24,experts=[4,5]; c6:bw=55,experts=[0,4,5,6,7]; c0:bw=30,experts=[3,4,5]; c4:bw=18,experts=[1]; c7:bw=44,experts=[4,5,6,7]; c3:bw=28,experts=[3,4]; c1:bw=72,experts=[0,1,2,3,4,5,6]; c9:bw=43,experts=[4,5,6,7]</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>2.4922,2.8485,8.2560,9.7000,4.3845,7.5075,12.8444,1.3991,11.4927,3.2800</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:02:02</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0.5784213313858079</v>
+      </c>
+      <c r="F88" t="n">
+        <v>93.95359557467732</v>
+      </c>
+      <c r="G88" t="n">
+        <v>95.42102028272895</v>
+      </c>
+      <c r="H88" t="n">
+        <v>77</v>
+      </c>
+      <c r="I88" t="n">
+        <v>68.4423</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>1:08.44</t>
+        </is>
+      </c>
+      <c r="K88" t="n">
+        <v>64.3922</v>
+      </c>
+      <c r="L88" t="n">
+        <v>1.2709</v>
+      </c>
+      <c r="M88" t="n">
+        <v>2.7783</v>
+      </c>
+      <c r="N88" t="n">
+        <v>6007.7596</v>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>1:40:07.76</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>1,2,7,5,6,3,4,9,8,0</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>1:29;2:67;7:22;5:10;6:60;3:68;4:34;9:37;8:46;0:35</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>1:[0,7];2:[0,1,2,3,6,7];7:[0,1];5:[2];6:[1,2,3,4,5,6];3:[0,1,2,5,6,7];4:[2,3,4];9:[0,1,2];8:[0,5,6,7];0:[0,6,7]</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>c1:bw=29,experts=[0,7]; c2:bw=67,experts=[0,1,2,3,6,7]; c7:bw=22,experts=[0,1]; c5:bw=10,experts=[2]; c6:bw=60,experts=[1,2,3,4,5,6]; c3:bw=68,experts=[0,1,2,5,6,7]; c4:bw=34,experts=[2,3,4]; c9:bw=37,experts=[0,1,2]; c8:bw=46,experts=[0,5,6,7]; c0:bw=35,experts=[0,6,7]</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>11.4616,8.3121,12.9526,2.4867,9.6467,1.3961,7.5719,3.2914,2.8608,4.4123</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:03:10</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0.5768095792077341</v>
+      </c>
+      <c r="F89" t="n">
+        <v>94.69114935464044</v>
+      </c>
+      <c r="G89" t="n">
+        <v>95.42102028272895</v>
+      </c>
+      <c r="H89" t="n">
+        <v>77</v>
+      </c>
+      <c r="I89" t="n">
+        <v>68.2182</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>1:08.22</t>
+        </is>
+      </c>
+      <c r="K89" t="n">
+        <v>64.1728</v>
+      </c>
+      <c r="L89" t="n">
+        <v>1.2744</v>
+      </c>
+      <c r="M89" t="n">
+        <v>2.7702</v>
+      </c>
+      <c r="N89" t="n">
+        <v>6076.0118</v>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>1:41:16.01</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>8,6,3,7,0,4,9,1,5,2</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>8:43;6:27;3:33;7:41;0:62;4:38;9:31;1:28;5:30;2:46</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>8:[1,2,3,4];6:[0,7];3:[3,4,5];7:[2,3,4,5];0:[1,2,3,4,5,6];4:[5,6,7];9:[3,4,5];1:[1,2];5:[3,4,5];2:[4,5,6,7]</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>c8:bw=43,experts=[1,2,3,4]; c6:bw=27,experts=[0,7]; c3:bw=33,experts=[3,4,5]; c7:bw=41,experts=[2,3,4,5]; c0:bw=62,experts=[1,2,3,4,5,6]; c4:bw=38,experts=[5,6,7]; c9:bw=31,experts=[3,4,5]; c1:bw=28,experts=[1,2]; c5:bw=30,experts=[3,4,5]; c2:bw=46,experts=[4,5,6,7]</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>2.8386,9.7221,1.3946,12.9425,4.4136,7.5524,3.2758,11.3456,2.4732,8.2143</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:04:18</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0.5788170177090237</v>
+      </c>
+      <c r="F90" t="n">
+        <v>93.85371850030731</v>
+      </c>
+      <c r="G90" t="n">
+        <v>95.42102028272895</v>
+      </c>
+      <c r="H90" t="n">
+        <v>77</v>
+      </c>
+      <c r="I90" t="n">
+        <v>68.2411</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>1:08.24</t>
+        </is>
+      </c>
+      <c r="K90" t="n">
+        <v>64.21769999999999</v>
+      </c>
+      <c r="L90" t="n">
+        <v>1.2423</v>
+      </c>
+      <c r="M90" t="n">
+        <v>2.7803</v>
+      </c>
+      <c r="N90" t="n">
+        <v>6144.2871</v>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>1:42:24.29</t>
+        </is>
+      </c>
+      <c r="P90" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>3,8,2,9,7,5,0,6,4,1</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>3:31;8:74;2:44;9:60;7:21;5:46;0:13;6:32;4:30;1:41</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>3:[0,6,7];8:[0,1,2,3,5,6,7];2:[0,1,2,3];9:[0,1,2,3,6,7];7:[6,7];5:[0,1,6,7];0:[7];6:[1,2,3];4:[0,1,2];1:[3,4,5,6]</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>c3:bw=31,experts=[0,6,7]; c8:bw=74,experts=[0,1,2,3,5,6,7]; c2:bw=44,experts=[0,1,2,3]; c9:bw=60,experts=[0,1,2,3,6,7]; c7:bw=21,experts=[6,7]; c5:bw=46,experts=[0,1,6,7]; c0:bw=13,experts=[7]; c6:bw=32,experts=[1,2,3]; c4:bw=30,experts=[0,1,2]; c1:bw=41,experts=[3,4,5,6]</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>1.3984,2.8822,8.3571,3.3183,12.8748,2.5047,4.3774,9.6360,7.5473,11.3215</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:05:27</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0.5763431176872095</v>
+      </c>
+      <c r="F91" t="n">
+        <v>94.3338967424708</v>
+      </c>
+      <c r="G91" t="n">
+        <v>95.42102028272895</v>
+      </c>
+      <c r="H91" t="n">
+        <v>77</v>
+      </c>
+      <c r="I91" t="n">
+        <v>68.2435</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>1:08.24</t>
+        </is>
+      </c>
+      <c r="K91" t="n">
+        <v>64.2296</v>
+      </c>
+      <c r="L91" t="n">
+        <v>1.2955</v>
+      </c>
+      <c r="M91" t="n">
+        <v>2.7175</v>
+      </c>
+      <c r="N91" t="n">
+        <v>6212.5645</v>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>1:43:32.56</t>
+        </is>
+      </c>
+      <c r="P91" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>7,1,3,9,0,6,2,5,8,4</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>7:72;1:31;3:36;9:63;0:64;6:26;2:21;5:27;8:50;4:35</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>7:[0,1,2,3,4,5,6];1:[0,1,7];3:[1,2,3];9:[0,1,4,5,6,7];0:[0,1,2,3,4,5];6:[4,5];2:[4,5];5:[2,3];8:[0,4,5,6,7];4:[3,4,5]</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>c7:bw=72,experts=[0,1,2,3,4,5,6]; c1:bw=31,experts=[0,1,7]; c3:bw=36,experts=[1,2,3]; c9:bw=63,experts=[0,1,4,5,6,7]; c0:bw=64,experts=[0,1,2,3,4,5]; c6:bw=26,experts=[4,5]; c2:bw=21,experts=[4,5]; c5:bw=27,experts=[2,3]; c8:bw=50,experts=[0,4,5,6,7]; c4:bw=35,experts=[3,4,5]</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>13.0611,11.4515,1.3963,3.2686,4.4224,9.5923,8.2242,2.4830,2.8349,7.4954</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:06:35</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0.5757324754046353</v>
+      </c>
+      <c r="F92" t="n">
+        <v>94.38383527965581</v>
+      </c>
+      <c r="G92" t="n">
+        <v>95.42102028272895</v>
+      </c>
+      <c r="H92" t="n">
+        <v>77</v>
+      </c>
+      <c r="I92" t="n">
+        <v>68.20189999999999</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>1:08.20</t>
+        </is>
+      </c>
+      <c r="K92" t="n">
+        <v>64.19119999999999</v>
+      </c>
+      <c r="L92" t="n">
+        <v>1.2347</v>
+      </c>
+      <c r="M92" t="n">
+        <v>2.7752</v>
+      </c>
+      <c r="N92" t="n">
+        <v>6280.8006</v>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>1:44:40.80</t>
+        </is>
+      </c>
+      <c r="P92" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>1,9,5,7,3,4,0,6,2,8</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>1:50;9:35;5:52;7:51;3:40;4:54;0:22;6:29;2:11;8:23</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>1:[2,3,4,5,6];9:[2,3,4];5:[0,4,5,6,7];7:[0,1,2,3,7];3:[4,5,6,7];4:[0,1,2,6,7];0:[6,7];6:[6,7];2:[6];8:[1,2]</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>c1:bw=50,experts=[2,3,4,5,6]; c9:bw=35,experts=[2,3,4]; c5:bw=52,experts=[0,4,5,6,7]; c7:bw=51,experts=[0,1,2,3,7]; c3:bw=40,experts=[4,5,6,7]; c4:bw=54,experts=[0,1,2,6,7]; c0:bw=22,experts=[6,7]; c6:bw=29,experts=[6,7]; c2:bw=11,experts=[6]; c8:bw=23,experts=[1,2]</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>11.5229,3.2969,2.4986,12.9296,1.3796,7.5555,4.3786,9.6009,8.2053,2.8235</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:07:43</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0.5784383569083105</v>
+      </c>
+      <c r="F93" t="n">
+        <v>94.66041794714198</v>
+      </c>
+      <c r="G93" t="n">
+        <v>95.42102028272895</v>
+      </c>
+      <c r="H93" t="n">
+        <v>77</v>
+      </c>
+      <c r="I93" t="n">
+        <v>68.1992</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>1:08.20</t>
+        </is>
+      </c>
+      <c r="K93" t="n">
+        <v>64.2183</v>
+      </c>
+      <c r="L93" t="n">
+        <v>1.1818</v>
+      </c>
+      <c r="M93" t="n">
+        <v>2.7984</v>
+      </c>
+      <c r="N93" t="n">
+        <v>6349.0345</v>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>1:45:49.03</t>
+        </is>
+      </c>
+      <c r="P93" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>3,7,1,0,8,6,9,2,5,4</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>3:28;7:34;1:20;0:29;8:19;6:45;9:56;2:25;5:66;4:26</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>3:[0,1];7:[4,5,6];1:[0,7];0:[0,1];8:[3];6:[0,1,2,3];9:[0,1,5,6,7];2:[0,7];5:[1,2,3,4,5,6];4:[3,4]</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>c3:bw=28,experts=[0,1]; c7:bw=34,experts=[4,5,6]; c1:bw=20,experts=[0,7]; c0:bw=29,experts=[0,1]; c8:bw=19,experts=[3]; c6:bw=45,experts=[0,1,2,3]; c9:bw=56,experts=[0,1,5,6,7]; c2:bw=25,experts=[0,7]; c5:bw=66,experts=[1,2,3,4,5,6]; c4:bw=26,experts=[3,4]</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>1.4077,12.9250,11.4590,4.4139,2.8221,9.6463,3.2813,8.2388,2.4860,7.5382</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:08:51</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0.5756115096746564</v>
+      </c>
+      <c r="F94" t="n">
+        <v>94.34926244622004</v>
+      </c>
+      <c r="G94" t="n">
+        <v>95.42102028272895</v>
+      </c>
+      <c r="H94" t="n">
+        <v>77</v>
+      </c>
+      <c r="I94" t="n">
+        <v>68.15179999999999</v>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>1:08.15</t>
+        </is>
+      </c>
+      <c r="K94" t="n">
+        <v>64.17700000000001</v>
+      </c>
+      <c r="L94" t="n">
+        <v>1.1983</v>
+      </c>
+      <c r="M94" t="n">
+        <v>2.7757</v>
+      </c>
+      <c r="N94" t="n">
+        <v>6417.2212</v>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>1:46:57.22</t>
+        </is>
+      </c>
+      <c r="P94" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>1,3,7,9,6,8,5,4,0,2</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>1:47;3:31;7:22;9:58;6:22;8:10;5:10;4:32;0:19;2:51</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>1:[1,2,3,4];3:[2,3,4];7:[0,7];9:[2,3,4,5,6];6:[4,5];8:[4];5:[7];4:[5,6,7];0:[2];2:[1,2,3,4,5]</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>c1:bw=47,experts=[1,2,3,4]; c3:bw=31,experts=[2,3,4]; c7:bw=22,experts=[0,7]; c9:bw=58,experts=[2,3,4,5,6]; c6:bw=22,experts=[4,5]; c8:bw=10,experts=[4]; c5:bw=10,experts=[7]; c4:bw=32,experts=[5,6,7]; c0:bw=19,experts=[2]; c2:bw=51,experts=[1,2,3,4,5]</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>11.4315,1.3921,12.9679,3.2968,9.6671,2.8155,2.4500,7.5203,4.3901,8.2456</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:10:00</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0.57578479090472</v>
+      </c>
+      <c r="F95" t="n">
+        <v>95.04840196681008</v>
+      </c>
+      <c r="G95" t="n">
+        <v>95.42102028272895</v>
+      </c>
+      <c r="H95" t="n">
+        <v>77</v>
+      </c>
+      <c r="I95" t="n">
+        <v>68.4123</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>1:08.41</t>
+        </is>
+      </c>
+      <c r="K95" t="n">
+        <v>64.32089999999999</v>
+      </c>
+      <c r="L95" t="n">
+        <v>1.2977</v>
+      </c>
+      <c r="M95" t="n">
+        <v>2.7928</v>
+      </c>
+      <c r="N95" t="n">
+        <v>6485.6689</v>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>1:48:05.67</t>
+        </is>
+      </c>
+      <c r="P95" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>7,2,5,4,6,9,1,8,0,3</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>7:45;2:65;5:41;4:31;6:30;9:50;1:70;8:10;0:55;3:34</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>7:[1,2,3,4];2:[0,1,2,3,6,7];5:[0,1,2,3];4:[0,1,2];6:[0,6,7];9:[0,1,2,3,7];1:[0,1,2,3,5,6,7];8:[5];0:[3,4,5,6,7];3:[5,6,7]</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>c7:bw=45,experts=[1,2,3,4]; c2:bw=65,experts=[0,1,2,3,6,7]; c5:bw=41,experts=[0,1,2,3]; c4:bw=31,experts=[0,1,2]; c6:bw=30,experts=[0,6,7]; c9:bw=50,experts=[0,1,2,3,7]; c1:bw=70,experts=[0,1,2,3,5,6,7]; c8:bw=10,experts=[5]; c0:bw=55,experts=[3,4,5,6,7]; c3:bw=34,experts=[5,6,7]</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>12.9317,8.3321,2.5132,7.6198,9.6463,3.2945,11.4008,2.8224,4.3594,1.4007</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:11:08</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0.5775848251348499</v>
+      </c>
+      <c r="F96" t="n">
+        <v>93.81914566687155</v>
+      </c>
+      <c r="G96" t="n">
+        <v>95.42102028272895</v>
+      </c>
+      <c r="H96" t="n">
+        <v>77</v>
+      </c>
+      <c r="I96" t="n">
+        <v>68.2253</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>1:08.23</t>
+        </is>
+      </c>
+      <c r="K96" t="n">
+        <v>64.27630000000001</v>
+      </c>
+      <c r="L96" t="n">
+        <v>1.233</v>
+      </c>
+      <c r="M96" t="n">
+        <v>2.7152</v>
+      </c>
+      <c r="N96" t="n">
+        <v>6553.9298</v>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>1:49:13.93</t>
+        </is>
+      </c>
+      <c r="P96" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>7,9,4,6,0,3,1,8,2,5</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>7:59;9:42;4:15;6:40;0:35;3:41;1:31;8:76;2:23;5:10</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>7:[0,1,5,6,7];9:[4,5,6,7];4:[3];6:[1,2,3,4];0:[0,1,2];3:[0,1,2,3];1:[4,5,6];8:[0,1,2,3,4,6,7];2:[4,5];5:[4]</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>c7:bw=59,experts=[0,1,5,6,7]; c9:bw=42,experts=[4,5,6,7]; c4:bw=15,experts=[3]; c6:bw=40,experts=[1,2,3,4]; c0:bw=35,experts=[0,1,2]; c3:bw=41,experts=[0,1,2,3]; c1:bw=31,experts=[4,5,6]; c8:bw=76,experts=[0,1,2,3,4,6,7]; c2:bw=23,experts=[4,5]; c5:bw=10,experts=[4]</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>12.9117,3.2653,7.6280,9.7123,4.4282,1.4146,11.3823,2.8555,8.2041,2.4743</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:12:17</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0.5781637607443743</v>
+      </c>
+      <c r="F97" t="n">
+        <v>95.19053472649047</v>
+      </c>
+      <c r="G97" t="n">
+        <v>95.42102028272895</v>
+      </c>
+      <c r="H97" t="n">
+        <v>77</v>
+      </c>
+      <c r="I97" t="n">
+        <v>68.5594</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>1:08.56</t>
+        </is>
+      </c>
+      <c r="K97" t="n">
+        <v>64.398</v>
+      </c>
+      <c r="L97" t="n">
+        <v>1.3735</v>
+      </c>
+      <c r="M97" t="n">
+        <v>2.787</v>
+      </c>
+      <c r="N97" t="n">
+        <v>6622.5244</v>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>1:50:22.52</t>
+        </is>
+      </c>
+      <c r="P97" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>2,9,3,1,5,4,6,7,0,8</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>2:65;9:44;3:46;1:36;5:60;4:49;6:31;7:50;0:36;8:64</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>2:[0,1,2,3,6,7];9:[0,1,2,3];3:[4,5,6,7];1:[0,1,7];5:[0,1,2,5,6,7];4:[4,5,6,7];6:[5,6,7];7:[2,3,4,5,6];0:[3,4,5];8:[0,1,2,5,6,7]</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>c2:bw=65,experts=[0,1,2,3,6,7]; c9:bw=44,experts=[0,1,2,3]; c3:bw=46,experts=[4,5,6,7]; c1:bw=36,experts=[0,1,7]; c5:bw=60,experts=[0,1,2,5,6,7]; c4:bw=49,experts=[4,5,6,7]; c6:bw=31,experts=[5,6,7]; c7:bw=50,experts=[2,3,4,5,6]; c0:bw=36,experts=[3,4,5]; c8:bw=64,experts=[0,1,2,5,6,7]</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>8.3588,3.3046,1.4024,11.4594,2.5074,7.5768,9.6760,12.8991,4.3767,2.8368</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:13:25</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0.5748928765635041</v>
+      </c>
+      <c r="F98" t="n">
+        <v>94.69114935464044</v>
+      </c>
+      <c r="G98" t="n">
+        <v>95.42102028272895</v>
+      </c>
+      <c r="H98" t="n">
+        <v>77</v>
+      </c>
+      <c r="I98" t="n">
+        <v>68.3768</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>1:08.38</t>
+        </is>
+      </c>
+      <c r="K98" t="n">
+        <v>64.325</v>
+      </c>
+      <c r="L98" t="n">
+        <v>1.2728</v>
+      </c>
+      <c r="M98" t="n">
+        <v>2.7781</v>
+      </c>
+      <c r="N98" t="n">
+        <v>6690.9369</v>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>1:51:30.94</t>
+        </is>
+      </c>
+      <c r="P98" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>0,9,8,4,7,1,3,5,6,2</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>0:41;9:43;8:43;4:16;7:30;1:50;3:35;5:46;6:50;2:54</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>0:[0,1,6,7];9:[4,5,6,7];8:[3,4,5,6];4:[0];7:[0,1,7];1:[2,3,4,5,6];3:[0,1,2];5:[3,4,5,6];6:[0,1,2,3,4];2:[0,4,5,6,7]</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>c0:bw=41,experts=[0,1,6,7]; c9:bw=43,experts=[4,5,6,7]; c8:bw=43,experts=[3,4,5,6]; c4:bw=16,experts=[0]; c7:bw=30,experts=[0,1,7]; c1:bw=50,experts=[2,3,4,5,6]; c3:bw=35,experts=[0,1,2]; c5:bw=46,experts=[3,4,5,6]; c6:bw=50,experts=[0,1,2,3,4]; c2:bw=54,experts=[0,4,5,6,7]</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>4.4139,3.2842,2.8337,7.5979,12.9146,11.4449,1.3925,2.4723,9.6683,8.3026</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:14:33</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0.5745863208470955</v>
+      </c>
+      <c r="F99" t="n">
+        <v>94.4299323909035</v>
+      </c>
+      <c r="G99" t="n">
+        <v>95.42102028272895</v>
+      </c>
+      <c r="H99" t="n">
+        <v>77</v>
+      </c>
+      <c r="I99" t="n">
+        <v>68.2786</v>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>1:08.28</t>
+        </is>
+      </c>
+      <c r="K99" t="n">
+        <v>64.2837</v>
+      </c>
+      <c r="L99" t="n">
+        <v>1.2069</v>
+      </c>
+      <c r="M99" t="n">
+        <v>2.7872</v>
+      </c>
+      <c r="N99" t="n">
+        <v>6759.2514</v>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>1:52:39.25</t>
+        </is>
+      </c>
+      <c r="P99" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>4,8,9,7,6,5,0,3,1,2</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>4:52;8:54;9:27;7:24;6:36;5:49;0:33;3:25;1:26;2:24</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>4:[1,2,3,4,5];8:[0,1,2,3,7];9:[0,1];7:[2,3];6:[5,6,7];5:[0,1,2,7];0:[2,3,4];3:[3,4];1:[0,7];2:[1,2]</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>c4:bw=52,experts=[1,2,3,4,5]; c8:bw=54,experts=[0,1,2,3,7]; c9:bw=27,experts=[0,1]; c7:bw=24,experts=[2,3]; c6:bw=36,experts=[5,6,7]; c5:bw=49,experts=[0,1,2,7]; c0:bw=33,experts=[2,3,4]; c3:bw=25,experts=[3,4]; c1:bw=26,experts=[0,7]; c2:bw=24,experts=[1,2]</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>7.6087,2.8677,3.3093,12.9326,9.6170,2.5079,4.4100,1.4056,11.4052,8.2197</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:15:42</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0.5726064737430774</v>
+      </c>
+      <c r="F100" t="n">
+        <v>94.4798709280885</v>
+      </c>
+      <c r="G100" t="n">
+        <v>95.42102028272895</v>
+      </c>
+      <c r="H100" t="n">
+        <v>77</v>
+      </c>
+      <c r="I100" t="n">
+        <v>68.3438</v>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>1:08.34</t>
+        </is>
+      </c>
+      <c r="K100" t="n">
+        <v>64.3364</v>
+      </c>
+      <c r="L100" t="n">
+        <v>1.2603</v>
+      </c>
+      <c r="M100" t="n">
+        <v>2.7463</v>
+      </c>
+      <c r="N100" t="n">
+        <v>6827.632</v>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>1:53:47.63</t>
+        </is>
+      </c>
+      <c r="P100" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>8,5,7,1,3,9,4,0,2,6</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>8:34;5:49;7:45;1:59;3:38;9:20;4:24;0:40;2:31;6:35</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>8:[4,5,6];5:[3,4,5,6];7:[4,5,6,7];1:[1,2,3,4,5];3:[5,6,7];9:[2,3];4:[6,7];0:[0,5,6,7];2:[3,4,5];6:[0,1,2]</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>c8:bw=34,experts=[4,5,6]; c5:bw=49,experts=[3,4,5,6]; c7:bw=45,experts=[4,5,6,7]; c1:bw=59,experts=[1,2,3,4,5]; c3:bw=38,experts=[5,6,7]; c9:bw=20,experts=[2,3]; c4:bw=24,experts=[6,7]; c0:bw=40,experts=[0,5,6,7]; c2:bw=31,experts=[3,4,5]; c6:bw=35,experts=[0,1,2]</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>2.8663,2.4900,12.9211,11.4751,1.3894,3.3836,7.5238,4.3924,8.2307,9.6639</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2026-09-21 23:16:50</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0.5730364762536508</v>
+      </c>
+      <c r="F101" t="n">
+        <v>94.51060233558697</v>
+      </c>
+      <c r="G101" t="n">
+        <v>95.42102028272895</v>
+      </c>
+      <c r="H101" t="n">
+        <v>77</v>
+      </c>
+      <c r="I101" t="n">
+        <v>68.3062</v>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>1:08.31</t>
+        </is>
+      </c>
+      <c r="K101" t="n">
+        <v>64.2895</v>
+      </c>
+      <c r="L101" t="n">
+        <v>1.2397</v>
+      </c>
+      <c r="M101" t="n">
+        <v>2.7762</v>
+      </c>
+      <c r="N101" t="n">
+        <v>6895.9748</v>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>1:54:55.97</t>
+        </is>
+      </c>
+      <c r="P101" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>2,8,9,5,6,1,4,7,3,0</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>2:30;8:44;9:53;5:18;6:44;1:17;4:65;7:10;3:42;0:64</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>2:[0,6,7];8:[0,1,2,7];9:[0,4,5,6,7];5:[7];6:[3,4,5,6];1:[6];4:[0,1,2,3,4,5];7:[0];3:[0,1,2,3];0:[1,2,3,4,5,6]</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>c2:bw=30,experts=[0,6,7]; c8:bw=44,experts=[0,1,2,7]; c9:bw=53,experts=[0,4,5,6,7]; c5:bw=18,experts=[7]; c6:bw=44,experts=[3,4,5,6]; c1:bw=17,experts=[6]; c4:bw=65,experts=[0,1,2,3,4,5]; c7:bw=10,experts=[0]; c3:bw=42,experts=[0,1,2,3]; c0:bw=64,experts=[1,2,3,4,5,6]</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>8.2993,2.8769,3.3166,2.4832,9.6416,11.3963,7.5995,12.9088,1.3926,4.3748</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
